--- a/src/attributions/attributions_saliency_traj_53.xlsx
+++ b/src/attributions/attributions_saliency_traj_53.xlsx
@@ -999,2847 +999,2847 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.917183544719592e-05</v>
+        <v>0.0618203803896904</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003198691643774509</v>
+        <v>0.28615602850914</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002694145950954407</v>
+        <v>0.02061498537659645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001598208793438971</v>
+        <v>0.1826305389404297</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000526242598425597</v>
+        <v>0.06796427816152573</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001294734538532794</v>
+        <v>0.05318034067749977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001692365913186222</v>
+        <v>0.1018342524766922</v>
       </c>
       <c r="H2" t="n">
-        <v>9.564510401105508e-05</v>
+        <v>0.01016523782163858</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00013755849795416</v>
+        <v>0.03069812245666981</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003342087147757411</v>
+        <v>0.03001811541616917</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0027673973236233</v>
+        <v>0.3247125446796417</v>
       </c>
       <c r="L2" t="n">
-        <v>3.151705459458753e-05</v>
+        <v>0.05686268582940102</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001493796240538359</v>
+        <v>0.2371930181980133</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000524449220392853</v>
+        <v>0.07011156529188156</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001347203797195107</v>
+        <v>0.0704067274928093</v>
       </c>
       <c r="P2" t="n">
-        <v>8.275763684650883e-05</v>
+        <v>0.0199152585119009</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005759643972851336</v>
+        <v>0.1659817844629288</v>
       </c>
       <c r="R2" t="n">
-        <v>2.826280251611024e-06</v>
+        <v>0.05212457105517387</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001759147417033091</v>
+        <v>0.009302853606641293</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003998749889433384</v>
+        <v>0.07037683576345444</v>
       </c>
       <c r="U2" t="n">
-        <v>2.214124833699316e-05</v>
+        <v>0.001816094387322664</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0001766971254255623</v>
+        <v>0.03016340360045433</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0001445746020181105</v>
+        <v>0.05933766812086105</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0001696420658845454</v>
+        <v>0.001028805039823055</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002916814992204309</v>
+        <v>0.01040696538984776</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0002717215684242547</v>
+        <v>0.01588117331266403</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0002216384600615129</v>
+        <v>0.02491909265518188</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0003133970312774181</v>
+        <v>0.08286558091640472</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0004108697175979614</v>
+        <v>0.07765698432922363</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.69481378281489e-05</v>
+        <v>0.03182506561279297</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.000157424045028165</v>
+        <v>0.0166756808757782</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.906043689814396e-05</v>
+        <v>0.03076843172311783</v>
       </c>
       <c r="AG2" t="n">
-        <v>8.504359720973298e-05</v>
+        <v>0.004698634147644043</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.03564736188855e-05</v>
+        <v>0.05926299095153809</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.019471139647067e-05</v>
+        <v>0.02276545763015747</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5.533908915822394e-05</v>
+        <v>0.07380246371030807</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.000173650128999725</v>
+        <v>0.03904749825596809</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.000293798977509141</v>
+        <v>0.0566423088312149</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.763783777481876e-05</v>
+        <v>0.0532037541270256</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.64076753007248e-05</v>
+        <v>0.01631775870919228</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0002329298004042357</v>
+        <v>0.01990493945777416</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0002415658527752385</v>
+        <v>0.04516732320189476</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.000100300254416652</v>
+        <v>0.05692242830991745</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0001845545048126951</v>
+        <v>0.06367363780736923</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0001058879570337012</v>
+        <v>0.003447945695370436</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0001693186059128493</v>
+        <v>0.0252839233726263</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.001825029496103525</v>
+        <v>0.2602608501911163</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0002657186123542488</v>
+        <v>0.00934260431677103</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0006742021651007235</v>
+        <v>0.04767563194036484</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0001203545834869146</v>
+        <v>0.1222477853298187</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.10038880747743e-05</v>
+        <v>0.006945108063519001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0002242844639113173</v>
+        <v>0.04639975354075432</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.135591633617878e-05</v>
+        <v>0.008688269183039665</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0001009640545817092</v>
+        <v>0.04852575063705444</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0001211855706060305</v>
+        <v>0.02005093358457088</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0005918836104683578</v>
+        <v>0.00961137842386961</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0004696848045568913</v>
+        <v>0.02632544934749603</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0002260215405840427</v>
+        <v>0.09402745217084885</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0002462136617396027</v>
+        <v>0.02003935910761356</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.312238575541414e-05</v>
+        <v>0.0293585192412138</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0002308634720975533</v>
+        <v>0.03880244866013527</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0004340953892096877</v>
+        <v>0.004609696567058563</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.488159250584431e-05</v>
+        <v>0.02547920309007168</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0002255980944028124</v>
+        <v>0.001909188460558653</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0001052666484611109</v>
+        <v>0.04768513515591621</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0001611814514035359</v>
+        <v>0.01577641256153584</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0001452612341381609</v>
+        <v>0.04365333542227745</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0003928433288820088</v>
+        <v>0.04887007549405098</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.868887718766928e-05</v>
+        <v>0.001946076052263379</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0001886738609755412</v>
+        <v>0.1070665642619133</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.779347702628002e-06</v>
+        <v>0.02043858170509338</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.000159013201482594</v>
+        <v>0.0006097531877458096</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0001877815520856529</v>
+        <v>0.03945081681013107</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.001047726138494909</v>
+        <v>0.19270358979702</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0003183881344739348</v>
+        <v>0.006293518003076315</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0004332947137299925</v>
+        <v>0.07204478979110718</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0001045410608639941</v>
+        <v>0.0196819044649601</v>
       </c>
       <c r="BZ2" t="n">
-        <v>6.207953265402466e-05</v>
+        <v>0.01277382113039494</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0001214329386129975</v>
+        <v>0.009043401107192039</v>
       </c>
       <c r="CB2" t="n">
-        <v>9.804953879211098e-05</v>
+        <v>0.003682064823806286</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.0001044980745064095</v>
+        <v>0.01236391626298428</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.174374382477254e-05</v>
+        <v>0.01490917801856995</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0005164562608115375</v>
+        <v>0.0840141698718071</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0001257577387150377</v>
+        <v>0.02136453986167908</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0001666300086071715</v>
+        <v>0.04333842173218727</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.000131349399453029</v>
+        <v>0.003133704653009772</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.682571903278586e-06</v>
+        <v>0.006832591257989407</v>
       </c>
       <c r="CJ2" t="n">
-        <v>7.196470687631518e-05</v>
+        <v>0.03524935245513916</v>
       </c>
       <c r="CK2" t="n">
-        <v>4.0984323277371e-05</v>
+        <v>0.006563090719282627</v>
       </c>
       <c r="CL2" t="n">
-        <v>9.637414041208103e-05</v>
+        <v>0.004389441106468439</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.0006347123999148607</v>
+        <v>0.1692399680614471</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0001562873949296772</v>
+        <v>0.164155587553978</v>
       </c>
       <c r="CO2" t="n">
-        <v>5.19656423421111e-05</v>
+        <v>0.01142467185854912</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0003424859896767884</v>
+        <v>0.1051211059093475</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.0008469785680063069</v>
+        <v>0.00867525115609169</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0003701765672303736</v>
+        <v>0.03707684949040413</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0003356169036123902</v>
+        <v>0.02120817825198174</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.0003045950434170663</v>
+        <v>0.06155737861990929</v>
       </c>
       <c r="CU2" t="n">
-        <v>7.232147618196905e-05</v>
+        <v>0.01452964916825294</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.173189568566158e-05</v>
+        <v>0.02140140160918236</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0005477194208651781</v>
+        <v>0.0720779150724411</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0001907194236991927</v>
+        <v>0.0006098384037613869</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.000257955223787576</v>
+        <v>0.04081587865948677</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.000118165131425485</v>
+        <v>0.005784959997981787</v>
       </c>
       <c r="DA2" t="n">
-        <v>4.430145054357126e-05</v>
+        <v>0.0003633380401879549</v>
       </c>
       <c r="DB2" t="n">
-        <v>8.011647150851786e-05</v>
+        <v>0.02986790798604488</v>
       </c>
       <c r="DC2" t="n">
-        <v>7.37147347535938e-05</v>
+        <v>7.305014878511429e-05</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.287047290243208e-05</v>
+        <v>0.007733243983238935</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0003822215076070279</v>
+        <v>0.02508548833429813</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0004734107642434537</v>
+        <v>0.004383764695376158</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0001276527327718213</v>
+        <v>0.05794129893183708</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.0007991138263605535</v>
+        <v>0.05056368559598923</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0003773710632231086</v>
+        <v>0.1772790849208832</v>
       </c>
       <c r="DJ2" t="n">
-        <v>8.658837759867311e-05</v>
+        <v>0.1080087348818779</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.0001842365745687857</v>
+        <v>0.09001918137073517</v>
       </c>
       <c r="DL2" t="n">
-        <v>7.468068361049518e-05</v>
+        <v>0.03000799752771854</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.000174661647179164</v>
+        <v>0.0486777201294899</v>
       </c>
       <c r="DN2" t="n">
-        <v>9.693019092082977e-05</v>
+        <v>0.008451765403151512</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0003688831347972155</v>
+        <v>0.05933219939470291</v>
       </c>
       <c r="DP2" t="n">
-        <v>6.659796054009348e-05</v>
+        <v>0.0147605687379837</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.000217637381865643</v>
+        <v>0.06322109699249268</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0003566895902622491</v>
+        <v>0.01828042417764664</v>
       </c>
       <c r="DS2" t="n">
-        <v>9.303992555942386e-06</v>
+        <v>0.03150946646928787</v>
       </c>
       <c r="DT2" t="n">
-        <v>8.766612882027403e-05</v>
+        <v>0.0251680426299572</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0001185096480185166</v>
+        <v>0.009740393608808517</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0001130192467826419</v>
+        <v>0.02929632365703583</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0001640741247683764</v>
+        <v>0.06335849314928055</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0004543358809314668</v>
+        <v>0.038084976375103</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.160751895047724e-05</v>
+        <v>0.006479092873632908</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.000112994690425694</v>
+        <v>0.0225002970546484</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.000342814193572849</v>
+        <v>0.01523552462458611</v>
       </c>
       <c r="EB2" t="n">
-        <v>6.163308717077598e-05</v>
+        <v>0.0689653754234314</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.0001269035419682041</v>
+        <v>0.05383353307843208</v>
       </c>
       <c r="ED2" t="n">
-        <v>3.90151581086684e-05</v>
+        <v>0.001861344557255507</v>
       </c>
       <c r="EE2" t="n">
-        <v>2.343076812394429e-05</v>
+        <v>0.06779174506664276</v>
       </c>
       <c r="EF2" t="n">
-        <v>6.642079097218812e-05</v>
+        <v>0.01379130966961384</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0003358713875059038</v>
+        <v>0.07739107310771942</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0002444734855089337</v>
+        <v>0.03976619243621826</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0002749432169366628</v>
+        <v>0.06005023419857025</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0002524774754419923</v>
+        <v>0.005524892825633287</v>
       </c>
       <c r="EK2" t="n">
-        <v>3.136037776130252e-05</v>
+        <v>0.003941632807254791</v>
       </c>
       <c r="EL2" t="n">
-        <v>6.19192433077842e-05</v>
+        <v>0.02452962286770344</v>
       </c>
       <c r="EM2" t="n">
-        <v>4.279954009689391e-05</v>
+        <v>0.003040457610040903</v>
       </c>
       <c r="EN2" t="n">
-        <v>3.363585710758343e-05</v>
+        <v>0.005416338331997395</v>
       </c>
       <c r="EO2" t="n">
-        <v>3.910388841177337e-05</v>
+        <v>0.005725051276385784</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0004903143853880465</v>
+        <v>0.07705274224281311</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.0003166606184095144</v>
+        <v>0.02412509918212891</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0002402391255600378</v>
+        <v>0.03358382731676102</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0001598251546965912</v>
+        <v>0.02273216098546982</v>
       </c>
       <c r="ET2" t="n">
-        <v>1.436571074009407e-05</v>
+        <v>0.03137993067502975</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.000252296740654856</v>
+        <v>0.0309164859354496</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0003440259606577456</v>
+        <v>0.01429491955786943</v>
       </c>
       <c r="EW2" t="n">
-        <v>9.380653864354827e-06</v>
+        <v>0.05669140815734863</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0001051909566740505</v>
+        <v>0.02245261892676353</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.0005590274813584983</v>
+        <v>0.0994148924946785</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0001242928265128285</v>
+        <v>0.008794253692030907</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0001726109039736912</v>
+        <v>0.05051663890480995</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0001205902590299957</v>
+        <v>0.0147191509604454</v>
       </c>
       <c r="FC2" t="n">
-        <v>4.371438262751326e-05</v>
+        <v>0.0001164226559922099</v>
       </c>
       <c r="FD2" t="n">
-        <v>9.271114686271176e-05</v>
+        <v>0.04487486556172371</v>
       </c>
       <c r="FE2" t="n">
-        <v>4.133563197683543e-05</v>
+        <v>0.005267705768346786</v>
       </c>
       <c r="FF2" t="n">
-        <v>9.692822641227394e-05</v>
+        <v>0.005995020270347595</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0001112951067625545</v>
+        <v>0.03474129363894463</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0002067153982352465</v>
+        <v>0.04031966626644135</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0002162675664294511</v>
+        <v>0.01548604015260935</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0002005805290536955</v>
+        <v>0.08580037951469421</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.000294836878310889</v>
+        <v>0.002345478162169456</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0001335860724793747</v>
+        <v>0.02749720215797424</v>
       </c>
       <c r="FM2" t="n">
-        <v>7.141393143683672e-05</v>
+        <v>0.004322722554206848</v>
       </c>
       <c r="FN2" t="n">
-        <v>5.838603829033673e-05</v>
+        <v>0.03879692777991295</v>
       </c>
       <c r="FO2" t="n">
-        <v>6.180621130624786e-05</v>
+        <v>0.03341692686080933</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0003041699819732457</v>
+        <v>0.02295307070016861</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0002543561859056354</v>
+        <v>0.1360752731561661</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.0003055000852327794</v>
+        <v>0.02278994768857956</v>
       </c>
       <c r="FS2" t="n">
-        <v>3.998929241788574e-05</v>
+        <v>0.086789570748806</v>
       </c>
       <c r="FT2" t="n">
-        <v>5.910321124247275e-05</v>
+        <v>0.09884646534919739</v>
       </c>
       <c r="FU2" t="n">
-        <v>9.839373524300754e-05</v>
+        <v>0.08727655559778214</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.23040699691046e-05</v>
+        <v>0.0808202400803566</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0001172098418464884</v>
+        <v>0.04245967417955399</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0001648445904720575</v>
+        <v>0.03655289113521576</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0002864075649995357</v>
+        <v>0.01026398316025734</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.0001562438992550597</v>
+        <v>0.06250110268592834</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0001044172531692311</v>
+        <v>0.009681540541350842</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0001284466125071049</v>
+        <v>0.05745281279087067</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0003727229486685246</v>
+        <v>0.03814278542995453</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.0002657506556715816</v>
+        <v>0.00477155577391386</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0004374017589725554</v>
+        <v>0.07713328301906586</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0001524339313618839</v>
+        <v>0.06154733523726463</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0001635080698179081</v>
+        <v>0.03060284629464149</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.056321343639866e-05</v>
+        <v>0.05102239176630974</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001889776031021029</v>
+        <v>0.290529727935791</v>
       </c>
       <c r="C3" t="n">
-        <v>1.73262942553265e-05</v>
+        <v>0.02563681080937386</v>
       </c>
       <c r="D3" t="n">
-        <v>8.876379433786497e-05</v>
+        <v>0.07469987869262695</v>
       </c>
       <c r="E3" t="n">
-        <v>2.308810326212551e-05</v>
+        <v>0.05911264568567276</v>
       </c>
       <c r="F3" t="n">
-        <v>3.099597051914316e-06</v>
+        <v>0.03719290345907211</v>
       </c>
       <c r="G3" t="n">
-        <v>9.23103198147146e-06</v>
+        <v>0.07079488039016724</v>
       </c>
       <c r="H3" t="n">
-        <v>4.946286026097368e-06</v>
+        <v>0.07875092327594757</v>
       </c>
       <c r="I3" t="n">
-        <v>8.603006790508516e-06</v>
+        <v>0.04227737709879875</v>
       </c>
       <c r="J3" t="n">
-        <v>2.436797149130143e-05</v>
+        <v>0.01798509620130062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001686682662693784</v>
+        <v>0.3232755362987518</v>
       </c>
       <c r="L3" t="n">
-        <v>4.675298441725317e-06</v>
+        <v>0.04718548431992531</v>
       </c>
       <c r="M3" t="n">
-        <v>8.955942030297592e-05</v>
+        <v>0.1890399605035782</v>
       </c>
       <c r="N3" t="n">
-        <v>2.772757216007449e-05</v>
+        <v>0.1209591552615166</v>
       </c>
       <c r="O3" t="n">
-        <v>6.849602868896909e-06</v>
+        <v>0.01129571534693241</v>
       </c>
       <c r="P3" t="n">
-        <v>2.009257696045097e-05</v>
+        <v>0.0334123782813549</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.281621684436686e-05</v>
+        <v>0.01985258981585503</v>
       </c>
       <c r="R3" t="n">
-        <v>9.893619790091179e-08</v>
+        <v>0.05969716608524323</v>
       </c>
       <c r="S3" t="n">
-        <v>8.346685717697255e-06</v>
+        <v>0.004269083961844444</v>
       </c>
       <c r="T3" t="n">
-        <v>2.161143311241176e-05</v>
+        <v>0.0760834738612175</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98228599401773e-06</v>
+        <v>0.01810458488762379</v>
       </c>
       <c r="V3" t="n">
-        <v>1.518372027931036e-05</v>
+        <v>0.04396122321486473</v>
       </c>
       <c r="W3" t="n">
-        <v>3.859793196170358e-06</v>
+        <v>0.05800672248005867</v>
       </c>
       <c r="X3" t="n">
-        <v>8.597830856160726e-06</v>
+        <v>0.01556462328881025</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.048555077431956e-05</v>
+        <v>0.03915040194988251</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.12025479413569e-05</v>
+        <v>0.003962691407650709</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.492043096135603e-06</v>
+        <v>0.001133388839662075</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.035246663785074e-05</v>
+        <v>0.01192604750394821</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.296033562743105e-05</v>
+        <v>0.05096312612295151</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.264869741949951e-06</v>
+        <v>0.007729529403150082</v>
       </c>
       <c r="AE3" t="n">
-        <v>9.746541763888672e-06</v>
+        <v>0.06765837967395782</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.156069993157871e-05</v>
+        <v>0.104099914431572</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.375231017344049e-06</v>
+        <v>0.0103297084569931</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.191421339783119e-06</v>
+        <v>0.003219838254153728</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.451234185078647e-06</v>
+        <v>0.1129525601863861</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.925915734726004e-06</v>
+        <v>0.01740879192948341</v>
       </c>
       <c r="AK3" t="n">
-        <v>6.435274372051936e-06</v>
+        <v>0.0003017457202076912</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.812456685001962e-05</v>
+        <v>0.0634094700217247</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.484240551188122e-06</v>
+        <v>0.02042634785175323</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.020316504873335e-06</v>
+        <v>0.0179294366389513</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.115270581271034e-05</v>
+        <v>0.04077558219432831</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.704590067674872e-05</v>
+        <v>0.01451990194618702</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.191494811791927e-05</v>
+        <v>0.03223509341478348</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.101708095229696e-06</v>
+        <v>0.05095409601926804</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.988061962445499e-06</v>
+        <v>0.0295383520424366</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.924056050484069e-05</v>
+        <v>0.0007528681308031082</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0001167629816336557</v>
+        <v>0.3580502271652222</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.413195761619136e-05</v>
+        <v>0.001100936206057668</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.506959885475226e-05</v>
+        <v>0.04546475782990456</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.434516318317037e-05</v>
+        <v>0.1419379711151123</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.079805679182755e-05</v>
+        <v>0.03624255582690239</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.09697769707418e-06</v>
+        <v>0.02150158584117889</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.904191887864727e-06</v>
+        <v>0.003996440209448338</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.675657808344113e-06</v>
+        <v>0.0114851500838995</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.079577128228266e-06</v>
+        <v>0.01788901537656784</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.590856067603454e-05</v>
+        <v>0.03541531786322594</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.281482349848375e-05</v>
+        <v>0.007422979921102524</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.126588469764101e-06</v>
+        <v>0.03089285083115101</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.910908278863644e-06</v>
+        <v>0.02751430869102478</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.04327828012174e-05</v>
+        <v>0.03490375727415085</v>
       </c>
       <c r="BI3" t="n">
-        <v>7.3951632657554e-06</v>
+        <v>0.02827637083828449</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2.231723738077562e-05</v>
+        <v>0.05159777775406837</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.297231372329406e-06</v>
+        <v>0.06946814060211182</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.74191936821444e-05</v>
+        <v>0.02436413615942001</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.660081943555269e-05</v>
+        <v>0.08967435359954834</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.320868068432901e-05</v>
+        <v>0.04550034180283546</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.874013822904089e-06</v>
+        <v>0.02385599911212921</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.520200309343636e-05</v>
+        <v>0.0816076397895813</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.785529876651708e-06</v>
+        <v>0.0001937355846166611</v>
       </c>
       <c r="BR3" t="n">
-        <v>8.117375728033949e-06</v>
+        <v>0.09795276075601578</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01313989944174e-05</v>
+        <v>0.004827258642762899</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.616439582605381e-06</v>
+        <v>0.001506952568888664</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.050699756888207e-05</v>
+        <v>0.0303608812391758</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.428788765333593e-05</v>
+        <v>0.213213637471199</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.031617805187125e-05</v>
+        <v>0.006316868122667074</v>
       </c>
       <c r="BX3" t="n">
-        <v>3.117247251793742e-05</v>
+        <v>0.08083298802375793</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.823105544142891e-06</v>
+        <v>0.03245082870125771</v>
       </c>
       <c r="BZ3" t="n">
-        <v>8.424347470281646e-06</v>
+        <v>0.009783278219401836</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.153849188995082e-05</v>
+        <v>0.05776309221982956</v>
       </c>
       <c r="CB3" t="n">
-        <v>7.856313459342346e-06</v>
+        <v>0.01183493249118328</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.10212340587168e-06</v>
+        <v>0.03617848455905914</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.770467062873649e-06</v>
+        <v>0.005810019560158253</v>
       </c>
       <c r="CE3" t="n">
-        <v>3.053832551813684e-05</v>
+        <v>0.07263266295194626</v>
       </c>
       <c r="CF3" t="n">
-        <v>4.328000613895711e-06</v>
+        <v>0.0232720859348774</v>
       </c>
       <c r="CG3" t="n">
-        <v>8.808380698610563e-06</v>
+        <v>0.01964004524052143</v>
       </c>
       <c r="CH3" t="n">
-        <v>8.888014235708397e-06</v>
+        <v>0.01930327340960503</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.204082193202339e-06</v>
+        <v>0.002784886863082647</v>
       </c>
       <c r="CJ3" t="n">
-        <v>4.898962743027369e-06</v>
+        <v>0.01241451688110828</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.289242845814442e-08</v>
+        <v>0.0222872868180275</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.744473479448061e-06</v>
+        <v>0.001280880533158779</v>
       </c>
       <c r="CM3" t="n">
-        <v>5.807373236166313e-05</v>
+        <v>0.08996213972568512</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.790161695680581e-05</v>
+        <v>0.1741545349359512</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.901939867821056e-06</v>
+        <v>0.01913923397660255</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.706093800952658e-05</v>
+        <v>0.1287041306495667</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.573123806039803e-05</v>
+        <v>0.03637216240167618</v>
       </c>
       <c r="CR3" t="n">
-        <v>2.083837352984119e-05</v>
+        <v>0.03300322219729424</v>
       </c>
       <c r="CS3" t="n">
-        <v>1.675638850429095e-05</v>
+        <v>0.01806007325649261</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.974837298097555e-05</v>
+        <v>0.01502835378050804</v>
       </c>
       <c r="CU3" t="n">
-        <v>3.61274055649119e-06</v>
+        <v>0.007437271997332573</v>
       </c>
       <c r="CV3" t="n">
-        <v>4.180710106993502e-07</v>
+        <v>0.02545367553830147</v>
       </c>
       <c r="CW3" t="n">
-        <v>3.178941915393807e-05</v>
+        <v>0.06542500853538513</v>
       </c>
       <c r="CX3" t="n">
-        <v>9.555379619996529e-06</v>
+        <v>0.01734394021332264</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.551488639961462e-05</v>
+        <v>0.02693708427250385</v>
       </c>
       <c r="CZ3" t="n">
-        <v>7.65505956223933e-06</v>
+        <v>0.00541398674249649</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.703680595710466e-06</v>
+        <v>0.009266695007681847</v>
       </c>
       <c r="DB3" t="n">
-        <v>5.333730769052636e-06</v>
+        <v>0.002337487414479256</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.391623638686724e-06</v>
+        <v>0.01653271540999413</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.616022917820374e-07</v>
+        <v>0.007894530892372131</v>
       </c>
       <c r="DE3" t="n">
-        <v>2.201247298216913e-05</v>
+        <v>0.04526550322771072</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.245770156150684e-05</v>
+        <v>0.03008436411619186</v>
       </c>
       <c r="DG3" t="n">
-        <v>4.835176696360577e-06</v>
+        <v>0.06346888840198517</v>
       </c>
       <c r="DH3" t="n">
-        <v>3.623538941610605e-05</v>
+        <v>0.07046502083539963</v>
       </c>
       <c r="DI3" t="n">
-        <v>2.744603807514068e-05</v>
+        <v>0.1252467930316925</v>
       </c>
       <c r="DJ3" t="n">
-        <v>6.186589871504111e-06</v>
+        <v>0.1228877827525139</v>
       </c>
       <c r="DK3" t="n">
-        <v>1.619789691176265e-05</v>
+        <v>0.02256457880139351</v>
       </c>
       <c r="DL3" t="n">
-        <v>1.168410562968347e-06</v>
+        <v>0.0291758831590414</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.43383294926025e-05</v>
+        <v>0.01675836928188801</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.81211707968032e-05</v>
+        <v>0.01268737576901913</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.19121175177861e-05</v>
+        <v>0.0582137331366539</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.065996891877148e-06</v>
+        <v>0.03326286375522614</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.209452420880552e-05</v>
+        <v>0.0758671909570694</v>
       </c>
       <c r="DR3" t="n">
-        <v>1.810785215639044e-05</v>
+        <v>0.001863200217485428</v>
       </c>
       <c r="DS3" t="n">
-        <v>1.017898853206134e-06</v>
+        <v>0.005027315113693476</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.51339290823671e-05</v>
+        <v>0.002076186239719391</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.436535037821159e-07</v>
+        <v>0.002946021035313606</v>
       </c>
       <c r="DV3" t="n">
-        <v>1.651048137318867e-06</v>
+        <v>0.04940242692828178</v>
       </c>
       <c r="DW3" t="n">
-        <v>2.217750079580583e-05</v>
+        <v>0.02211597189307213</v>
       </c>
       <c r="DX3" t="n">
-        <v>4.064671884407289e-05</v>
+        <v>0.008135458454489708</v>
       </c>
       <c r="DY3" t="n">
-        <v>1.857989673226257e-06</v>
+        <v>0.002608185634016991</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.217965836985968e-05</v>
+        <v>0.03714142367243767</v>
       </c>
       <c r="EA3" t="n">
-        <v>2.539626802899875e-05</v>
+        <v>0.03788179904222488</v>
       </c>
       <c r="EB3" t="n">
-        <v>8.711513146408834e-06</v>
+        <v>0.0375693291425705</v>
       </c>
       <c r="EC3" t="n">
-        <v>5.201321528147673e-06</v>
+        <v>0.02135270833969116</v>
       </c>
       <c r="ED3" t="n">
-        <v>7.902212018962018e-06</v>
+        <v>0.06221530959010124</v>
       </c>
       <c r="EE3" t="n">
-        <v>2.410188471912988e-06</v>
+        <v>0.03884711861610413</v>
       </c>
       <c r="EF3" t="n">
-        <v>9.000227692013141e-07</v>
+        <v>0.02614920027554035</v>
       </c>
       <c r="EG3" t="n">
-        <v>2.46180370595539e-05</v>
+        <v>0.03202048316597939</v>
       </c>
       <c r="EH3" t="n">
-        <v>1.199350936076371e-05</v>
+        <v>0.0162622444331646</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.43434072015225e-05</v>
+        <v>0.08142420649528503</v>
       </c>
       <c r="EJ3" t="n">
-        <v>1.280331980524352e-05</v>
+        <v>0.03107835724949837</v>
       </c>
       <c r="EK3" t="n">
-        <v>8.449617325823056e-07</v>
+        <v>0.03090481460094452</v>
       </c>
       <c r="EL3" t="n">
-        <v>6.00819703322486e-06</v>
+        <v>0.004993913229554892</v>
       </c>
       <c r="EM3" t="n">
-        <v>8.904783499019686e-06</v>
+        <v>0.0001235911622643471</v>
       </c>
       <c r="EN3" t="n">
-        <v>1.5229203427225e-06</v>
+        <v>0.01190591603517532</v>
       </c>
       <c r="EO3" t="n">
-        <v>5.633592081721872e-06</v>
+        <v>0.01773970946669579</v>
       </c>
       <c r="EP3" t="n">
-        <v>3.205711618647911e-05</v>
+        <v>0.03216566517949104</v>
       </c>
       <c r="EQ3" t="n">
-        <v>1.750321098370478e-05</v>
+        <v>0.01175994705408812</v>
       </c>
       <c r="ER3" t="n">
-        <v>3.204471795470454e-06</v>
+        <v>0.02436133474111557</v>
       </c>
       <c r="ES3" t="n">
-        <v>5.938353751844261e-06</v>
+        <v>0.01472613029181957</v>
       </c>
       <c r="ET3" t="n">
-        <v>1.205179796670564e-05</v>
+        <v>0.0524367019534111</v>
       </c>
       <c r="EU3" t="n">
-        <v>1.828082895372063e-05</v>
+        <v>0.002272144425660372</v>
       </c>
       <c r="EV3" t="n">
-        <v>1.073596467904281e-05</v>
+        <v>0.002286897040903568</v>
       </c>
       <c r="EW3" t="n">
-        <v>7.251661827467615e-06</v>
+        <v>0.02162820100784302</v>
       </c>
       <c r="EX3" t="n">
-        <v>6.559226221725112e-06</v>
+        <v>0.008273459039628506</v>
       </c>
       <c r="EY3" t="n">
-        <v>3.358691174071282e-05</v>
+        <v>0.08586136996746063</v>
       </c>
       <c r="EZ3" t="n">
-        <v>6.243471489142394e-06</v>
+        <v>0.01114676613360643</v>
       </c>
       <c r="FA3" t="n">
-        <v>9.645402315072715e-06</v>
+        <v>0.03587563708424568</v>
       </c>
       <c r="FB3" t="n">
-        <v>3.760117579076905e-06</v>
+        <v>0.01015918515622616</v>
       </c>
       <c r="FC3" t="n">
-        <v>1.268317305402888e-06</v>
+        <v>0.00468780193477869</v>
       </c>
       <c r="FD3" t="n">
-        <v>4.966759206581628e-06</v>
+        <v>0.01818550378084183</v>
       </c>
       <c r="FE3" t="n">
-        <v>9.636737559048925e-07</v>
+        <v>0.01940382272005081</v>
       </c>
       <c r="FF3" t="n">
-        <v>1.55649422595161e-06</v>
+        <v>0.006273495033383369</v>
       </c>
       <c r="FG3" t="n">
-        <v>6.264916919462848e-06</v>
+        <v>0.01019883342087269</v>
       </c>
       <c r="FH3" t="n">
-        <v>3.345934237586334e-05</v>
+        <v>0.05785263329744339</v>
       </c>
       <c r="FI3" t="n">
-        <v>1.200291444547474e-05</v>
+        <v>0.007113562431186438</v>
       </c>
       <c r="FJ3" t="n">
-        <v>1.290132058784366e-05</v>
+        <v>0.05551660060882568</v>
       </c>
       <c r="FK3" t="n">
-        <v>2.293386933160946e-05</v>
+        <v>0.01526651158928871</v>
       </c>
       <c r="FL3" t="n">
-        <v>1.56837995746173e-05</v>
+        <v>0.03678369149565697</v>
       </c>
       <c r="FM3" t="n">
-        <v>7.186123184510507e-06</v>
+        <v>0.01380784995853901</v>
       </c>
       <c r="FN3" t="n">
-        <v>2.216955181211233e-06</v>
+        <v>0.0008848570287227631</v>
       </c>
       <c r="FO3" t="n">
-        <v>7.60059538151836e-06</v>
+        <v>0.07415370643138885</v>
       </c>
       <c r="FP3" t="n">
-        <v>2.14072824746836e-05</v>
+        <v>0.02161511592566967</v>
       </c>
       <c r="FQ3" t="n">
-        <v>2.02191995413159e-06</v>
+        <v>0.1326444447040558</v>
       </c>
       <c r="FR3" t="n">
-        <v>1.984917071240488e-05</v>
+        <v>0.02267149277031422</v>
       </c>
       <c r="FS3" t="n">
-        <v>1.227588427354931e-06</v>
+        <v>0.06303635984659195</v>
       </c>
       <c r="FT3" t="n">
-        <v>5.077115019958001e-06</v>
+        <v>0.1234587356448174</v>
       </c>
       <c r="FU3" t="n">
-        <v>9.5320747277583e-06</v>
+        <v>0.04466307163238525</v>
       </c>
       <c r="FV3" t="n">
-        <v>3.286591891082935e-06</v>
+        <v>0.00664258748292923</v>
       </c>
       <c r="FW3" t="n">
-        <v>1.324076947639696e-05</v>
+        <v>0.03683153539896011</v>
       </c>
       <c r="FX3" t="n">
-        <v>1.452114247513236e-05</v>
+        <v>0.003949555568397045</v>
       </c>
       <c r="FY3" t="n">
-        <v>1.790814349078573e-05</v>
+        <v>0.0286050159484148</v>
       </c>
       <c r="FZ3" t="n">
-        <v>8.191069355234504e-06</v>
+        <v>0.03279103711247444</v>
       </c>
       <c r="GA3" t="n">
-        <v>1.596840320416959e-06</v>
+        <v>0.04574908316135406</v>
       </c>
       <c r="GB3" t="n">
-        <v>8.727791282581165e-06</v>
+        <v>0.003023015335202217</v>
       </c>
       <c r="GC3" t="n">
-        <v>2.81462280327105e-06</v>
+        <v>0.02439621835947037</v>
       </c>
       <c r="GD3" t="n">
-        <v>1.682470247033052e-05</v>
+        <v>0.01057781931012869</v>
       </c>
       <c r="GE3" t="n">
-        <v>1.330974828306353e-05</v>
+        <v>0.04610079154372215</v>
       </c>
       <c r="GF3" t="n">
-        <v>4.1733542275324e-06</v>
+        <v>0.01939581707119942</v>
       </c>
       <c r="GG3" t="n">
-        <v>8.159108801919501e-06</v>
+        <v>0.01545363012701273</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.007602333556860685</v>
+        <v>0.1040002256631851</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1730914562940598</v>
+        <v>0.03291632235050201</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05770048499107361</v>
+        <v>0.3670364320278168</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02095343172550201</v>
+        <v>0.004757676273584366</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0899372324347496</v>
+        <v>0.4178631603717804</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02061914093792439</v>
+        <v>0.08981578052043915</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04952551797032356</v>
+        <v>0.1804498434066772</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001622044946998358</v>
+        <v>0.07461767643690109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008661631494760513</v>
+        <v>0.1861893087625504</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03382992744445801</v>
+        <v>0.0002776370383799076</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1318192481994629</v>
+        <v>0.1272976696491241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06477047502994537</v>
+        <v>0.4528065919876099</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06239933520555496</v>
+        <v>0.08056844025850296</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07239469885826111</v>
+        <v>0.4380059540271759</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01327496487647295</v>
+        <v>0.1744456142187119</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04661689698696136</v>
+        <v>0.1163841187953949</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02542959526181221</v>
+        <v>0.02637780085206032</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02554322220385075</v>
+        <v>0.08753564953804016</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007194783538579941</v>
+        <v>0.03277162462472916</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01654300838708878</v>
+        <v>0.02096362411975861</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01084611937403679</v>
+        <v>0.01007507927715778</v>
       </c>
       <c r="V4" t="n">
-        <v>3.012164961546659e-05</v>
+        <v>0.004087811335921288</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001194561831653118</v>
+        <v>0.02862966805696487</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01455536670982838</v>
+        <v>0.04809203371405602</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001352917053736746</v>
+        <v>0.04514159634709358</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03061969578266144</v>
+        <v>0.05886348709464073</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01743360050022602</v>
+        <v>0.1521703451871872</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009087318321689963</v>
+        <v>0.01576421409845352</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01839491538703442</v>
+        <v>0.006103007588535547</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004612157121300697</v>
+        <v>0.02860050462186337</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.001004557125270367</v>
+        <v>0.1415027678012848</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03856251016259193</v>
+        <v>0.1095990464091301</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02125874906778336</v>
+        <v>0.09288918972015381</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0180953610688448</v>
+        <v>0.09358024597167969</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03283042833209038</v>
+        <v>0.06907185167074203</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01071753539144993</v>
+        <v>0.01638190075755119</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03523334488272667</v>
+        <v>0.006357188336551189</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01368278451263905</v>
+        <v>0.08171336352825165</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.01046431064605713</v>
+        <v>0.03574978187680244</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.03610505908727646</v>
+        <v>0.02147085219621658</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.02032938227057457</v>
+        <v>0.04299040138721466</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.01754540391266346</v>
+        <v>0.08029494434595108</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002425553742796183</v>
+        <v>0.01071309670805931</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.008186131715774536</v>
+        <v>0.07915443927049637</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.008796791546046734</v>
+        <v>0.003099054098129272</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.02299546636641026</v>
+        <v>0.1167408004403114</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1270668506622314</v>
+        <v>0.3714452981948853</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.03116544336080551</v>
+        <v>0.05655557289719582</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.02306990511715412</v>
+        <v>0.1447382569313049</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.02172203734517097</v>
+        <v>0.1666153818368912</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.03366502374410629</v>
+        <v>0.1008746773004532</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0549486055970192</v>
+        <v>0.0004412382841110229</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.05136226117610931</v>
+        <v>0.005353629589080811</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0293031744658947</v>
+        <v>0.03011071123182774</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.04108484461903572</v>
+        <v>0.01020704209804535</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.04408601671457291</v>
+        <v>0.2702032923698425</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.02056244201958179</v>
+        <v>0.1597080677747726</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01960084028542042</v>
+        <v>0.01229641027748585</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03857405856251717</v>
+        <v>0.090424545109272</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.02286379411816597</v>
+        <v>0.1045499294996262</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.002058071549981833</v>
+        <v>0.003944924101233482</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.005622410215437412</v>
+        <v>0.06702809780836105</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.02006747201085091</v>
+        <v>0.1162380874156952</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.01903863251209259</v>
+        <v>0.08637043088674545</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03861859068274498</v>
+        <v>0.04999139159917831</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01133417338132858</v>
+        <v>0.04664873331785202</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.006509737111628056</v>
+        <v>0.07356500625610352</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002628771355375648</v>
+        <v>0.1646912693977356</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01347718946635723</v>
+        <v>0.03370029479265213</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.01067821495234966</v>
+        <v>0.2364725321531296</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002034746110439301</v>
+        <v>0.04563750326633453</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.008049106225371361</v>
+        <v>0.02241872437298298</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01669218204915524</v>
+        <v>0.08110017329454422</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.06482629477977753</v>
+        <v>0.09521129727363586</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.04329654201865196</v>
+        <v>0.0605103112757206</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001776803168468177</v>
+        <v>0.07341906428337097</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.008166687563061714</v>
+        <v>0.02478426322340965</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0009181371424347162</v>
+        <v>0.02212386205792427</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.01703378185629845</v>
+        <v>0.08168203383684158</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01412045210599899</v>
+        <v>0.004269298166036606</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.006769037339836359</v>
+        <v>0.1111715510487556</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.006207943893969059</v>
+        <v>0.06551460176706314</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.02711929380893707</v>
+        <v>0.06825744360685349</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.004568648990243673</v>
+        <v>0.07092900574207306</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004258741624653339</v>
+        <v>0.01031994447112083</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01217750366777182</v>
+        <v>0.04161690920591354</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.006147651933133602</v>
+        <v>0.001146395690739155</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.01711027137935162</v>
+        <v>0.02555698342621326</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.008361288346350193</v>
+        <v>0.01937488839030266</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.004453914240002632</v>
+        <v>0.008545189164578915</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.05216000974178314</v>
+        <v>0.05919331684708595</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0260110180824995</v>
+        <v>0.08331578969955444</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0214849691838026</v>
+        <v>0.003199498169124126</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.006570746190845966</v>
+        <v>0.1645898669958115</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01024149730801582</v>
+        <v>0.2301176488399506</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.01550587639212608</v>
+        <v>0.1566862910985947</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.02803390100598335</v>
+        <v>0.1116377413272858</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.01421994157135487</v>
+        <v>0.01849192753434181</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.006883929017931223</v>
+        <v>0.02124501205980778</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.004080244340002537</v>
+        <v>0.06670639663934708</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0316828079521656</v>
+        <v>0.05692000687122345</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.008741286583244801</v>
+        <v>0.09317927807569504</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.01182693894952536</v>
+        <v>0.03594807907938957</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01449503842741251</v>
+        <v>0.06054376065731049</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.005333893932402134</v>
+        <v>0.01651477068662643</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01398082543164492</v>
+        <v>0.02230009436607361</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.01093620434403419</v>
+        <v>0.009749783203005791</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.002101497957482934</v>
+        <v>0.03694558888673782</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.05261761695146561</v>
+        <v>0.008300554007291794</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.03053736686706543</v>
+        <v>0.2144819349050522</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0127189988270402</v>
+        <v>0.1666599214076996</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.03805404528975487</v>
+        <v>0.0251364316791296</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.003373043611645699</v>
+        <v>0.1893037706613541</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.01355742290616035</v>
+        <v>0.2585967779159546</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0181150883436203</v>
+        <v>0.01479935832321644</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.01558551657944918</v>
+        <v>0.1231566518545151</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.02003347128629684</v>
+        <v>0.01221281290054321</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.02703210711479187</v>
+        <v>0.009130993857979774</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01476668752729893</v>
+        <v>0.07366138696670532</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.02022057399153709</v>
+        <v>0.0622737817466259</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.01356435194611549</v>
+        <v>0.08943726867437363</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.007593140006065369</v>
+        <v>0.08998490869998932</v>
       </c>
       <c r="DS4" t="n">
-        <v>3.882404416799545e-05</v>
+        <v>0.05279378592967987</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003078125417232513</v>
+        <v>0.08316050469875336</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0007897268515080214</v>
+        <v>0.005601633340120316</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.02739475481212139</v>
+        <v>0.02059340104460716</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0004118217620998621</v>
+        <v>0.01958794519305229</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05111805722117424</v>
+        <v>0.03882990032434464</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.00656016543507576</v>
+        <v>0.0373646542429924</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.001052222680300474</v>
+        <v>0.006281569600105286</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.01303846202790737</v>
+        <v>0.0121603962033987</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.005250408314168453</v>
+        <v>0.1324729919433594</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.003936379216611385</v>
+        <v>0.03888256475329399</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.01198593247681856</v>
+        <v>0.08722662180662155</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.01140613574534655</v>
+        <v>0.1142907813191414</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.004622363485395908</v>
+        <v>0.00554257445037365</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.01267183199524879</v>
+        <v>0.03357454389333725</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0006418232806026936</v>
+        <v>0.02756067737936974</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.00582455936819315</v>
+        <v>0.009852882474660873</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01297243870794773</v>
+        <v>0.05355476960539818</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0001168777234852314</v>
+        <v>0.006690395995974541</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.01286822557449341</v>
+        <v>0.02492101117968559</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.005250456742942333</v>
+        <v>0.0181573536247015</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.00184959452599287</v>
+        <v>0.01605043187737465</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.005860303994268179</v>
+        <v>0.1060043796896935</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.004995469935238361</v>
+        <v>0.01894473657011986</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01557054370641708</v>
+        <v>0.04154273867607117</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.02902752533555031</v>
+        <v>0.09302011132240295</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.03154421597719193</v>
+        <v>0.0284689087420702</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02521238476037979</v>
+        <v>0.03974795714020729</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.01724313944578171</v>
+        <v>0.06198184192180634</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.03062925860285759</v>
+        <v>0.007303787395358086</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.03171446546912193</v>
+        <v>0.02120162546634674</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.008972732350230217</v>
+        <v>0.0741993710398674</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.02454382367432117</v>
+        <v>0.09323278069496155</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.00506685022264719</v>
+        <v>0.07512563467025757</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.004282088950276375</v>
+        <v>0.03983594104647636</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01324646640568972</v>
+        <v>0.04340676218271255</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01029933802783489</v>
+        <v>0.01813812367618084</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.01910858973860741</v>
+        <v>0.0249802116304636</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.006055318750441074</v>
+        <v>0.01145228371024132</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.002829642966389656</v>
+        <v>0.03513872995972633</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.007471892051398754</v>
+        <v>0.06890393048524857</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.009443720802664757</v>
+        <v>0.03843502327799797</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.004392276983708143</v>
+        <v>0.06654323637485504</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.003229743801057339</v>
+        <v>0.02661737240850925</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.01167461276054382</v>
+        <v>0.02855346351861954</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.00841062143445015</v>
+        <v>0.1089376285672188</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.008278761990368366</v>
+        <v>0.1263549625873566</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.001938420347869396</v>
+        <v>0.05399543419480324</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0006494242697954178</v>
+        <v>0.01319972611963749</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.04355499893426895</v>
+        <v>0.06436546146869659</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.03272285312414169</v>
+        <v>0.06376348435878754</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.02730291709303856</v>
+        <v>0.03163310512900352</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.01760929077863693</v>
+        <v>0.07586240768432617</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.04558218270540237</v>
+        <v>0.05617048963904381</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.001085468102246523</v>
+        <v>0.06947281956672668</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.004738734103739262</v>
+        <v>0.03067243099212646</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.004058481194078922</v>
+        <v>0.02393749356269836</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.01911843940615654</v>
+        <v>0.01726717315614223</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.005593931302428246</v>
+        <v>0.1140511184930801</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.008157454431056976</v>
+        <v>0.008680220693349838</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.01113330945372581</v>
+        <v>0.0325736403465271</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.009904363192617893</v>
+        <v>0.09306834638118744</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.01702350564301014</v>
+        <v>0.1922637522220612</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.009775287471711636</v>
+        <v>0.07923789322376251</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.03176721185445786</v>
+        <v>0.1292419880628586</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.07731472700834274</v>
+        <v>0.08412230014801025</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0191475935280323</v>
+        <v>0.03972555696964264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.003191692987456918</v>
+        <v>2.850489181582816e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02090549096465111</v>
+        <v>2.138379204552621e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003844337072223425</v>
+        <v>6.684937488898868e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003323629731312394</v>
+        <v>5.15720785188023e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007170132361352444</v>
+        <v>7.871383786550723e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00163191044703126</v>
+        <v>3.324491217426839e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002172992099076509</v>
+        <v>2.810690148180583e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000666252279188484</v>
+        <v>1.439685547666159e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001938636763952672</v>
+        <v>1.583254970682901e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004352763760834932</v>
+        <v>4.394522079564922e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01618805155158043</v>
+        <v>2.435552232782356e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00291746761649847</v>
+        <v>6.664746251772158e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005636441055685282</v>
+        <v>1.968681544894935e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01028549578040838</v>
+        <v>9.776762453839183e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>9.417650289833546e-06</v>
+        <v>1.714754716886091e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004071712493896484</v>
+        <v>7.94794345893024e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001464143628254533</v>
+        <v>1.684008338997955e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001420306973159313</v>
+        <v>2.064768978016218e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000934476382099092</v>
+        <v>6.431599786083098e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004072769545018673</v>
+        <v>3.686940772240632e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001302009448409081</v>
+        <v>9.884280416372349e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006214457098394632</v>
+        <v>2.052775926131289e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001118571497499943</v>
+        <v>3.704715709318407e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004653513431549072</v>
+        <v>8.49205036956846e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0004706616164185107</v>
+        <v>1.154851247520128e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0007751850062049925</v>
+        <v>1.542422523925779e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001167501031886786</v>
+        <v>2.701237235669396e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002071383874863386</v>
+        <v>3.295508008704928e-07</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004540910944342613</v>
+        <v>1.17131946808513e-06</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001166059984825552</v>
+        <v>4.243784132995643e-06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001554433023557067</v>
+        <v>4.103825631318614e-06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001756836893036962</v>
+        <v>4.310772055760026e-06</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0004242623690515757</v>
+        <v>1.571487132423499e-06</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.001906749908812344</v>
+        <v>3.652970548273515e-08</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0006856428808532655</v>
+        <v>5.118227363709593e-06</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002188357757404447</v>
+        <v>3.247000677220058e-06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0002709478139877319</v>
+        <v>1.564786316521349e-06</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.004428047221153975</v>
+        <v>8.41911696625175e-06</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0006241409573704004</v>
+        <v>5.261141495793709e-07</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.002298663835972548</v>
+        <v>1.733247358970402e-07</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0007737060077488422</v>
+        <v>8.375061042897869e-06</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.003030208172276616</v>
+        <v>1.723971308820182e-06</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001395848812535405</v>
+        <v>1.379592958983267e-06</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001259697019122541</v>
+        <v>3.02217108583136e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.002715230453759432</v>
+        <v>6.080206560454826e-09</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.002110200468450785</v>
+        <v>2.274393182233325e-06</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01073153968900442</v>
+        <v>1.929875361383893e-05</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002096091862767935</v>
+        <v>1.25639360248897e-06</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0003525909851305187</v>
+        <v>2.129610038537066e-06</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0001740669831633568</v>
+        <v>2.36217601923272e-06</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.002451517852023244</v>
+        <v>1.221119646288571e-06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0007560265948995948</v>
+        <v>9.301346892698348e-08</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0002784573589451611</v>
+        <v>1.219233354277094e-06</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001615891931578517</v>
+        <v>1.893020112220256e-06</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0004536594497039914</v>
+        <v>3.010708269357565e-06</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.001732266042381525</v>
+        <v>3.100831008850946e-06</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.001335348468273878</v>
+        <v>5.618676368612796e-06</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.003752723801881075</v>
+        <v>1.921207513078116e-06</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.01012754812836647</v>
+        <v>9.550945833325386e-06</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.000545222545042634</v>
+        <v>7.401342827506596e-07</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.002051555551588535</v>
+        <v>1.490542672399897e-06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001784119987860322</v>
+        <v>1.244011627932196e-06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0004333763790782541</v>
+        <v>5.161950866749976e-07</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001960561145097017</v>
+        <v>1.060683189280098e-06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.003014486748725176</v>
+        <v>1.906934016915329e-06</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0001737473648972809</v>
+        <v>1.672900452831527e-06</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0006025297334417701</v>
+        <v>2.177470605602139e-06</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.003170990850776434</v>
+        <v>1.034637080010725e-06</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001866403734311461</v>
+        <v>3.827574630577146e-07</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001596686895936728</v>
+        <v>2.609344392112689e-06</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.002639683894813061</v>
+        <v>8.179823680620757e-07</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.002009857911616564</v>
+        <v>2.185625817219261e-06</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001547129242680967</v>
+        <v>2.982391833938891e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.006695147603750229</v>
+        <v>1.438526305719279e-05</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.003951959311962128</v>
+        <v>7.952794476295821e-07</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0007177243824116886</v>
+        <v>3.457470711509814e-06</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.329182123299688e-05</v>
+        <v>4.31684793511522e-06</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.298997762612998e-05</v>
+        <v>5.665484081873728e-08</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0009517645230516791</v>
+        <v>1.880830950540258e-06</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.002372077899053693</v>
+        <v>7.045933898552903e-07</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0008798300987109542</v>
+        <v>6.54822429169144e-07</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0006153289577923715</v>
+        <v>1.475494059377525e-06</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.004376555792987347</v>
+        <v>7.700304195168428e-06</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.000278878869721666</v>
+        <v>2.156485606974456e-06</v>
       </c>
       <c r="CG5" t="n">
-        <v>6.710461457259953e-05</v>
+        <v>7.08654454228963e-07</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0002318946062587202</v>
+        <v>1.079563958228391e-06</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001145923015428707</v>
+        <v>4.449673269846244e-07</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0003071668324992061</v>
+        <v>1.41097913797239e-07</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0001228877808898687</v>
+        <v>9.284044608648401e-07</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0008614802500233054</v>
+        <v>4.735834124858229e-08</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004295618738979101</v>
+        <v>3.043056494789198e-06</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001133180223405361</v>
+        <v>1.176743808173342e-05</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001397814601659775</v>
+        <v>3.400408786546905e-06</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0002475272631272674</v>
+        <v>5.9682297433028e-06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0001157358492491767</v>
+        <v>1.956279447767884e-06</v>
       </c>
       <c r="CR5" t="n">
-        <v>2.916096127592027e-05</v>
+        <v>3.884922534780344e-07</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.000823707552626729</v>
+        <v>1.018305511024664e-06</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0006727626314386725</v>
+        <v>1.811082142921805e-06</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.002628506626933813</v>
+        <v>1.442502252757549e-06</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007041348144412041</v>
+        <v>4.660126080580085e-07</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.00461524585261941</v>
+        <v>7.083352102199569e-06</v>
       </c>
       <c r="CX5" t="n">
-        <v>6.95091366651468e-05</v>
+        <v>1.75200511876028e-06</v>
       </c>
       <c r="CY5" t="n">
-        <v>6.473361281678081e-05</v>
+        <v>9.665926370416855e-08</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0005877531366422772</v>
+        <v>2.727867638441239e-07</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0005406691343523562</v>
+        <v>5.779853609055863e-07</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0005266014486551285</v>
+        <v>5.832770284541766e-07</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004336994607001543</v>
+        <v>1.438793219676882e-06</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0009652718435972929</v>
+        <v>9.710295216791565e-07</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.001099921530112624</v>
+        <v>1.115097802539822e-06</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.006045064888894558</v>
+        <v>4.377449840831105e-06</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001395343570038676</v>
+        <v>2.615651283122133e-06</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.003739450592547655</v>
+        <v>2.417042423985549e-06</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.003298301249742508</v>
+        <v>8.373922923965438e-07</v>
       </c>
       <c r="DJ5" t="n">
-        <v>6.791728083044291e-06</v>
+        <v>6.277527518250281e-06</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.000450287334388122</v>
+        <v>9.666509868111461e-07</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0002380647929385304</v>
+        <v>2.3293341655517e-06</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0004336851416155696</v>
+        <v>8.242386684287339e-08</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001140068285167217</v>
+        <v>5.467387609314756e-07</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.002375401556491852</v>
+        <v>3.283869318693178e-06</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0002628805232234299</v>
+        <v>1.76128219209204e-06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0002944550360552967</v>
+        <v>2.102178768836893e-06</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0003682502720039338</v>
+        <v>1.637603872950422e-06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.001600212650373578</v>
+        <v>2.656260676303646e-06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001286050071939826</v>
+        <v>2.762209874163091e-07</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.001052134088240564</v>
+        <v>4.385825832287082e-06</v>
       </c>
       <c r="DV5" t="n">
-        <v>1.151685137301683e-05</v>
+        <v>3.756239493668545e-06</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001491053029894829</v>
+        <v>2.944506604762864e-06</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.002666528569534421</v>
+        <v>5.162649358680937e-06</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.000211436185054481</v>
+        <v>1.920337126648519e-06</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002132741647073999</v>
+        <v>1.148891556113085e-06</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0001199168618768454</v>
+        <v>2.92745767183078e-06</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003074967069551349</v>
+        <v>3.942859621020034e-06</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0006321970140561461</v>
+        <v>7.806073085703247e-07</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0008344316738657653</v>
+        <v>3.474446657492081e-06</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0007826840737834573</v>
+        <v>3.067258376177051e-06</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0005981213180348277</v>
+        <v>8.216925948545395e-07</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.002554142149165273</v>
+        <v>4.783695203514071e-06</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0004789971862919629</v>
+        <v>2.950689577119192e-07</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001306038117036223</v>
+        <v>8.362508197023999e-08</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001397325890138745</v>
+        <v>4.371107706901967e-07</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0006256571505218744</v>
+        <v>5.405720457929419e-07</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001867593848146498</v>
+        <v>7.185616937022132e-07</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.00102876138407737</v>
+        <v>8.139811598084634e-07</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001179049024358392</v>
+        <v>1.169907591247465e-06</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0007280176505446434</v>
+        <v>1.754837057887926e-07</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.003515569726005197</v>
+        <v>5.507054083864205e-06</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001024961937218904</v>
+        <v>5.244696126283088e-07</v>
       </c>
       <c r="ER5" t="n">
-        <v>7.195392390713096e-05</v>
+        <v>9.480486937718524e-07</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0005563788581639528</v>
+        <v>7.740919727439177e-07</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.00203637545928359</v>
+        <v>8.493677796650445e-07</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.002493782434612513</v>
+        <v>5.940293021922116e-07</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.001188012072816491</v>
+        <v>2.83727899841324e-07</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001496131881140172</v>
+        <v>1.305018145103531e-06</v>
       </c>
       <c r="EX5" t="n">
-        <v>1.622486161068082e-05</v>
+        <v>1.161123122983554e-06</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.004825025331228971</v>
+        <v>8.295249244838487e-06</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0005541181890293956</v>
+        <v>1.986893494176911e-06</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0001518147182650864</v>
+        <v>7.536777957284357e-08</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0005173064419068396</v>
+        <v>1.336234731752484e-07</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0004797174769919366</v>
+        <v>6.612603442590625e-07</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0006085102795623243</v>
+        <v>1.244471548034198e-07</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0003947512595914304</v>
+        <v>1.338232550551766e-06</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0003319839015603065</v>
+        <v>8.441360250799335e-07</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.001603284850716591</v>
+        <v>4.208725101761956e-07</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.00125769164878875</v>
+        <v>1.816546955524245e-06</v>
       </c>
       <c r="FI5" t="n">
-        <v>8.468909072689712e-05</v>
+        <v>4.530925707513234e-06</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001094440463930368</v>
+        <v>6.164883643577923e-07</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002503458643332124</v>
+        <v>3.152952558593825e-06</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0006881447625346482</v>
+        <v>1.250126160812215e-06</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.001884752884507179</v>
+        <v>6.5907244106711e-07</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.001195312826894224</v>
+        <v>4.423079928983498e-07</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.001740129198879004</v>
+        <v>2.303512019352638e-06</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001069372519850731</v>
+        <v>6.011723598930985e-06</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001629391685128212</v>
+        <v>7.408243163808947e-06</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0016836958238855</v>
+        <v>2.209362492067157e-06</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0009902096353471279</v>
+        <v>7.338879868257209e-07</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.002888470655307174</v>
+        <v>4.11804376199143e-06</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.002305872272700071</v>
+        <v>6.386699624272296e-06</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0003556079464033246</v>
+        <v>1.528068196421373e-06</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0007874704897403717</v>
+        <v>1.792151124391239e-06</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001422773348167539</v>
+        <v>6.941712399566313e-06</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002376572694629431</v>
+        <v>8.006609846233914e-07</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0009838424157351255</v>
+        <v>5.123747541802004e-06</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0003457407583482563</v>
+        <v>2.197921048718854e-06</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001479462254792452</v>
+        <v>1.626870584914286e-07</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.009028764441609383</v>
+        <v>4.119770892430097e-06</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.003591419197618961</v>
+        <v>1.829892767091224e-06</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.003158476203680038</v>
+        <v>2.519441750337137e-06</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.001225306419655681</v>
+        <v>1.090436057893385e-06</v>
       </c>
       <c r="GG5" t="n">
-        <v>4.948955029249191e-05</v>
+        <v>8.260662980319466e-07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0001283430610783398</v>
+        <v>3.611982535289826e-08</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05188755318522453</v>
+        <v>1.548991690469848e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005819878540933132</v>
+        <v>2.072853177992329e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005854466464370489</v>
+        <v>5.50988801251151e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005234113894402981</v>
+        <v>5.467413544124611e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00660578953102231</v>
+        <v>1.153486977045759e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003297950606793165</v>
+        <v>3.312958440915281e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001727790688164532</v>
+        <v>1.349852674081831e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01863526925444603</v>
+        <v>1.169514831644847e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004262944217771292</v>
+        <v>5.312059414563919e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04343946278095245</v>
+        <v>8.428642672697606e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001459306222386658</v>
+        <v>1.709976871211438e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01158249564468861</v>
+        <v>9.084818941573758e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001122274319641292</v>
+        <v>1.472880910569074e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004737068898975849</v>
+        <v>1.074506030818156e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001933199819177389</v>
+        <v>6.175756794846166e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008312975987792015</v>
+        <v>7.70577344155754e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01493529044091702</v>
+        <v>8.107662807788074e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008840790833346546</v>
+        <v>2.669981391534293e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004359134938567877</v>
+        <v>3.568476003579235e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>0.004033361561596394</v>
+        <v>2.855639724685943e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.005994251929223537</v>
+        <v>5.480940501456644e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005319698248058558</v>
+        <v>6.583199052556665e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009166296571493149</v>
+        <v>9.216315532967201e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002016558777540922</v>
+        <v>8.651364069578449e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00152170704677701</v>
+        <v>4.675373332929667e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.005614547058939934</v>
+        <v>3.483575383711468e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004121084697544575</v>
+        <v>1.805979721325457e-08</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.008229522965848446</v>
+        <v>2.575287538775228e-09</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.001234635710716248</v>
+        <v>9.772344711223013e-09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003127169795334339</v>
+        <v>8.481951851990743e-08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.002406822051852942</v>
+        <v>4.702066291883966e-08</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0002226477954536676</v>
+        <v>3.073349574833628e-09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0005063007120043039</v>
+        <v>2.639842477947241e-08</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.004839040338993073</v>
+        <v>5.563006055808728e-08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.001854914589785039</v>
+        <v>2.090616746386331e-08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.002633330877870321</v>
+        <v>1.966446383505627e-08</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005453473422676325</v>
+        <v>4.172583700778887e-08</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0001005813101073727</v>
+        <v>1.08340261206763e-08</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.003244807478040457</v>
+        <v>8.541673679474115e-08</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.001452907221391797</v>
+        <v>3.388172942209167e-08</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.003632716601714492</v>
+        <v>1.770801105749342e-08</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001803961931727827</v>
+        <v>1.313800002122889e-08</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003571000183001161</v>
+        <v>1.356367551608173e-08</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.002960021141916513</v>
+        <v>3.683534366416552e-09</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.002945983316749334</v>
+        <v>5.55828982840012e-09</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03055822476744652</v>
+        <v>4.395673158796853e-08</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.001467322697862983</v>
+        <v>2.336057391971735e-08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001595322508364916</v>
+        <v>5.591218155132083e-08</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001790024223737419</v>
+        <v>8.388143868387488e-08</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.003641699906438589</v>
+        <v>1.219014578168753e-08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.006105702836066484</v>
+        <v>2.330873627442998e-08</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.001033464097417891</v>
+        <v>1.103487079490151e-08</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.006234892643988132</v>
+        <v>3.589894959077355e-08</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0006378414109349251</v>
+        <v>4.629378125287076e-08</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01130691822618246</v>
+        <v>9.380997312291584e-08</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.003815478412434459</v>
+        <v>2.090911266350304e-08</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.004152439069002867</v>
+        <v>5.956682613827979e-08</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01027574203908443</v>
+        <v>3.684773375312034e-08</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.00336689967662096</v>
+        <v>7.133113211210684e-09</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.003442363813519478</v>
+        <v>1.00028003657826e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.003516546916216612</v>
+        <v>6.64851151910284e-09</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.008324123919010162</v>
+        <v>7.435912863229532e-08</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.005318173207342625</v>
+        <v>6.252468764955665e-09</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.001223138300701976</v>
+        <v>7.186677208892434e-08</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0002317518810741603</v>
+        <v>5.812102354951776e-09</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.002489297650754452</v>
+        <v>5.843570249908225e-08</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.007867153733968735</v>
+        <v>1.043253039512138e-08</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.008035321719944477</v>
+        <v>1.12553806275173e-08</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.001064230804331601</v>
+        <v>7.730402984407192e-08</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.002366785192862153</v>
+        <v>9.153514390902728e-09</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.002774487482383847</v>
+        <v>2.45965203760079e-08</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.002571179298684001</v>
+        <v>1.853172904020539e-08</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01774974726140499</v>
+        <v>1.152625195288692e-08</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.00393914757296443</v>
+        <v>1.817624806221829e-08</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.002203012350946665</v>
+        <v>6.654892104052124e-08</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.005924898199737072</v>
+        <v>1.908097857494795e-08</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.006771954707801342</v>
+        <v>6.555050902079529e-08</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.00154706509783864</v>
+        <v>6.485301184966374e-10</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.001570728607475758</v>
+        <v>4.060458280719104e-08</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.006224384531378746</v>
+        <v>6.794705598167639e-08</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0002540870627854019</v>
+        <v>8.313259414194363e-09</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.009309870190918446</v>
+        <v>1.959036488585753e-08</v>
       </c>
       <c r="CF6" t="n">
-        <v>8.785153477219865e-05</v>
+        <v>1.248741199333381e-08</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0003280606761109084</v>
+        <v>2.26874448117087e-08</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.003128579817712307</v>
+        <v>2.37655513046775e-08</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.001328227343037724</v>
+        <v>3.237644818909757e-08</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0006533616688102484</v>
+        <v>2.155153389082898e-08</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0009904881007969379</v>
+        <v>2.261454135066288e-08</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.003939981106668711</v>
+        <v>3.753403987616366e-08</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.007941624149680138</v>
+        <v>2.328250658933939e-08</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.008957774378359318</v>
+        <v>3.842011508936594e-08</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0007631904445588589</v>
+        <v>2.9570788040445e-09</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.003781025297939777</v>
+        <v>2.747559868510052e-08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.01147882454097271</v>
+        <v>9.38350837031976e-08</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.00551933515816927</v>
+        <v>8.24937984589269e-08</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.003079255810007453</v>
+        <v>7.75785196083234e-08</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.002723761834204197</v>
+        <v>2.173041480091342e-08</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.002499416004866362</v>
+        <v>8.660924777359469e-08</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0005286522791720927</v>
+        <v>8.953153773916256e-09</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.01009780913591385</v>
+        <v>2.807747101485347e-08</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.00080010702367872</v>
+        <v>9.235039399868583e-09</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0003377661050762981</v>
+        <v>1.08501216899981e-08</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002797028981149197</v>
+        <v>2.863646919593066e-08</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.00293348915874958</v>
+        <v>4.147401000409445e-08</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.001027460559271276</v>
+        <v>2.649518826558506e-08</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0005867761792615056</v>
+        <v>2.060450299268268e-08</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.003902433440089226</v>
+        <v>3.127238912270514e-08</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.001542816869914532</v>
+        <v>1.950431105512962e-08</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.005191431380808353</v>
+        <v>9.054119942675243e-08</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.006540454924106598</v>
+        <v>7.432113591221423e-08</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.007162958383560181</v>
+        <v>3.563497585901132e-08</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.003431504592299461</v>
+        <v>2.578433466737806e-08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001054524444043636</v>
+        <v>9.081348650852306e-08</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0001633101783227175</v>
+        <v>4.099890205111478e-08</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.002512282691895962</v>
+        <v>1.426128619641531e-07</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.003132778219878674</v>
+        <v>3.080436528080099e-08</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.003504061140120029</v>
+        <v>3.237953194457077e-08</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0007380243041552603</v>
+        <v>5.417523141204583e-08</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0002413753245491534</v>
+        <v>1.450863873486696e-08</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.152127515524626e-05</v>
+        <v>6.592016887907448e-08</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0005317587638273835</v>
+        <v>2.698738832407344e-08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001327771227806807</v>
+        <v>1.870596122444113e-09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.002812306862324476</v>
+        <v>8.207328150433568e-09</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.002501070033758879</v>
+        <v>1.493927470619383e-08</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.00262824073433876</v>
+        <v>5.213748011101416e-08</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0008095913217402995</v>
+        <v>8.670484774597753e-09</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.001790752983652055</v>
+        <v>2.128760812070141e-08</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.001513311290182173</v>
+        <v>3.890805544415343e-08</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.002618514699861407</v>
+        <v>4.939090558764292e-08</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0007042058277875185</v>
+        <v>2.185371705820671e-08</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001061331829987466</v>
+        <v>5.063022001650097e-08</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001435390440747142</v>
+        <v>3.459501840552548e-08</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.002866236492991447</v>
+        <v>1.302802132840952e-07</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.001356490654870868</v>
+        <v>1.871412802501027e-09</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0007354174158535898</v>
+        <v>7.589505912619643e-09</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.01166471373289824</v>
+        <v>4.102666295580093e-08</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0007972022285684943</v>
+        <v>3.964406580792001e-09</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0016591667663306</v>
+        <v>2.221210415598307e-08</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0006787842721678317</v>
+        <v>1.509817160183502e-08</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0001630978658795357</v>
+        <v>6.530437701712799e-08</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0001029456616379321</v>
+        <v>3.317370911304351e-08</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.001349788159132004</v>
+        <v>6.942141084209652e-09</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.004265561234205961</v>
+        <v>5.088286769705519e-08</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.004270183388143778</v>
+        <v>1.390600079531623e-08</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.009311848320066929</v>
+        <v>1.666239413111725e-08</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.002219897462055087</v>
+        <v>2.597804282800098e-08</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0002358150668442249</v>
+        <v>3.388385039215791e-08</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.003746050409972668</v>
+        <v>1.400381854921307e-08</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.006168850697577</v>
+        <v>3.580490925969571e-08</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.00172347470652312</v>
+        <v>4.749378845758656e-08</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.002047068439424038</v>
+        <v>9.714991477949297e-09</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0005167591734789312</v>
+        <v>8.727663924901208e-08</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0008339289925061166</v>
+        <v>1.84382997758803e-08</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0110385837033391</v>
+        <v>1.8612134056184e-08</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.001037573325447738</v>
+        <v>1.580411179702423e-08</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0004143755650147796</v>
+        <v>1.177970254673255e-08</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.00378706376068294</v>
+        <v>3.061079922872523e-08</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.003700670320540667</v>
+        <v>2.425443490494672e-08</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0001149876115960069</v>
+        <v>2.881408889265913e-08</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0005364311509765685</v>
+        <v>2.454562419984541e-08</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.002852735575288534</v>
+        <v>3.498615441799302e-08</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.001566420076414943</v>
+        <v>3.487185651351865e-08</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.007018459029495716</v>
+        <v>1.590973219833813e-08</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.001729526207782328</v>
+        <v>6.232089067026436e-09</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0002637405996210873</v>
+        <v>6.361539561794416e-08</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.005621159449219704</v>
+        <v>9.773552278602438e-08</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.000254702870734036</v>
+        <v>1.940478711048854e-08</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.001252890797331929</v>
+        <v>2.414062905131686e-08</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.001396654406562448</v>
+        <v>1.325947351915602e-09</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0001180179533548653</v>
+        <v>2.850335611981336e-08</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001845333143137395</v>
+        <v>2.676008037383326e-08</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.002278481610119343</v>
+        <v>3.020587513447026e-08</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.009992517530918121</v>
+        <v>3.107448520722755e-08</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.002782335504889488</v>
+        <v>6.633982252424175e-09</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.004985833540558815</v>
+        <v>7.123691148080979e-08</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0003799723344855011</v>
+        <v>3.654228208915811e-08</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.004451630637049675</v>
+        <v>1.048916828949586e-07</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.005345350131392479</v>
+        <v>2.237511864677799e-08</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.002091976348310709</v>
+        <v>3.081272126337353e-08</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.005660842172801495</v>
+        <v>5.232501010254964e-08</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.005807749461382627</v>
+        <v>5.959848081715791e-08</v>
       </c>
       <c r="GA6" t="n">
-        <v>3.555964212864637e-05</v>
+        <v>3.54933362700649e-08</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.001194395474158227</v>
+        <v>2.461762704797366e-08</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.01796900108456612</v>
+        <v>9.753454932592831e-09</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.004477239213883877</v>
+        <v>1.254943970963041e-08</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.009713014587759972</v>
+        <v>1.258046999907947e-09</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.005895673297345638</v>
+        <v>9.983497761822946e-08</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.001904352568089962</v>
+        <v>5.78189656152972e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4413,2847 +4413,2847 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002910214941948652</v>
+        <v>0.06731294095516205</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05793688073754311</v>
+        <v>0.2321871966123581</v>
       </c>
       <c r="C8" t="n">
-        <v>0.006042501423507929</v>
+        <v>0.06756698340177536</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02703931741416454</v>
+        <v>0.1394019573926926</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01172941923141479</v>
+        <v>0.02241944149136543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004296516068279743</v>
+        <v>0.03954347595572472</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00404327129945159</v>
+        <v>0.08753469586372375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005030376836657524</v>
+        <v>0.04816212505102158</v>
       </c>
       <c r="I8" t="n">
-        <v>5.503982538357377e-05</v>
+        <v>0.04157599061727524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002306538401171565</v>
+        <v>0.03874177485704422</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04673435911536217</v>
+        <v>0.2118040323257446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00133074086625129</v>
+        <v>0.08775101602077484</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02511239424347878</v>
+        <v>0.1818082630634308</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01127402484416962</v>
+        <v>0.05676436796784401</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002760224975645542</v>
+        <v>0.02286234684288502</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001511991489678621</v>
+        <v>0.09664128720760345</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005682216957211494</v>
+        <v>0.008909269236028194</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00251066917553544</v>
+        <v>0.003553834976628423</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001428689574822783</v>
+        <v>0.01292555779218674</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009304486215114594</v>
+        <v>0.01795285195112228</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003892979817464948</v>
+        <v>0.004414868075400591</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002260115463286638</v>
+        <v>0.03089446946978569</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0005999321583658457</v>
+        <v>0.04055327549576759</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006554846651852131</v>
+        <v>0.04951988160610199</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003849013242870569</v>
+        <v>0.01954528875648975</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004834230989217758</v>
+        <v>0.008429239504039288</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004294125363230705</v>
+        <v>0.05391858145594597</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004917984828352928</v>
+        <v>0.02280819416046143</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006579416338354349</v>
+        <v>0.0009204745292663574</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002712011570110917</v>
+        <v>0.02735720947384834</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.003473534481599927</v>
+        <v>0.07996119558811188</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0006375520024448633</v>
+        <v>0.004124900791794062</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00396994361653924</v>
+        <v>0.01202290039509535</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002002338413149118</v>
+        <v>0.05257894843816757</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001087962416931987</v>
+        <v>0.0257671270519495</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.000960310164373368</v>
+        <v>0.005432902835309505</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0007846751250326633</v>
+        <v>0.002692523412406445</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.008404792286455631</v>
+        <v>0.06612102687358856</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0006228464189916849</v>
+        <v>0.01671623811125755</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002047181827947497</v>
+        <v>0.02661957032978535</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0007403992349281907</v>
+        <v>0.03825711086392403</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.005193212069571018</v>
+        <v>0.02875146456062794</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002874626545235515</v>
+        <v>0.01378718391060829</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.005772191099822521</v>
+        <v>0.01660146936774254</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002592273987829685</v>
+        <v>0.02028590440750122</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.005334858782589436</v>
+        <v>0.02392043545842171</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03554072976112366</v>
+        <v>0.1119284257292747</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0005387901328504086</v>
+        <v>0.005748976953327656</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.006441099103540182</v>
+        <v>0.03659779950976372</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001918480498716235</v>
+        <v>0.1042951196432114</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001279328716918826</v>
+        <v>0.01923547126352787</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.000133915338665247</v>
+        <v>0.01545602083206177</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004538137465715408</v>
+        <v>0.02225843258202076</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001798238372430205</v>
+        <v>0.0139608271420002</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.002158190356567502</v>
+        <v>0.04351528361439705</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.008065616711974144</v>
+        <v>0.05911802500486374</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.006881145294755697</v>
+        <v>0.03309444338083267</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.005103849805891514</v>
+        <v>0.009888937696814537</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01691998168826103</v>
+        <v>0.05298180505633354</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.003647035453468561</v>
+        <v>0.0334276370704174</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005968731828033924</v>
+        <v>0.009233894757926464</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.004861515481024981</v>
+        <v>0.02273964323103428</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0001311799860559404</v>
+        <v>0.05108090117573738</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.006838250439614058</v>
+        <v>0.02189474552869797</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0008258780580945313</v>
+        <v>0.0005606943741440773</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0006838629487901926</v>
+        <v>0.01168547570705414</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002185122575610876</v>
+        <v>0.01407124940305948</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0005663736956194043</v>
+        <v>0.01788089983165264</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.006540358997881413</v>
+        <v>0.0173338707536459</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0003919696900993586</v>
+        <v>0.02811689488589764</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001476827776059508</v>
+        <v>0.001085165189579129</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001840945798903704</v>
+        <v>0.01896002702414989</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.005753492005169392</v>
+        <v>0.01251849718391895</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02053223177790642</v>
+        <v>0.1001687794923782</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.00461149774491787</v>
+        <v>0.0194198340177536</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.00443798815831542</v>
+        <v>0.06383213400840759</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.004656139761209488</v>
+        <v>0.03592916950583458</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.003317549824714661</v>
+        <v>0.05708073079586029</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001554349786601961</v>
+        <v>0.03088145330548286</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.00180431641638279</v>
+        <v>0.02478964999318123</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003637413494288921</v>
+        <v>0.05713038891553879</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001450434327125549</v>
+        <v>0.02199548296630383</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.009484076872467995</v>
+        <v>0.0546962171792984</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001321920775808394</v>
+        <v>0.02588639594614506</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004064687993377447</v>
+        <v>0.0497644916176796</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002472818829119205</v>
+        <v>0.002737549832090735</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001301934593357146</v>
+        <v>0.00143842538818717</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.00214800052344799</v>
+        <v>0.0007521866355091333</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0002117424737662077</v>
+        <v>0.01524893473833799</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.00186921888962388</v>
+        <v>0.01423910539597273</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.007878164760768414</v>
+        <v>0.01417074166238308</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0009641000651754439</v>
+        <v>0.07438359409570694</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001536867464892566</v>
+        <v>0.02903439104557037</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.006929013878107071</v>
+        <v>0.0658232793211937</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.006675317883491516</v>
+        <v>0.02803319506347179</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.007522458676248789</v>
+        <v>0.03799691796302795</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.005856883246451616</v>
+        <v>0.05135050415992737</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.007069145329296589</v>
+        <v>0.0127554964274168</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001916278386488557</v>
+        <v>0.06371065974235535</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001038137474097311</v>
+        <v>0.01390831917524338</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.009277150966227055</v>
+        <v>0.05156368762254715</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.002746617654338479</v>
+        <v>0.02234241366386414</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.005438823718577623</v>
+        <v>0.05328324809670448</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002564082620665431</v>
+        <v>0.0009992545237764716</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002223052317276597</v>
+        <v>0.0002450892934575677</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002053209580481052</v>
+        <v>0.009161191061139107</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.00103658577427268</v>
+        <v>0.01363146770745516</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0006329796742647886</v>
+        <v>0.01372405886650085</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.001745898160152137</v>
+        <v>0.02683200687170029</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.01534865330904722</v>
+        <v>0.07023938000202179</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0008685300126671791</v>
+        <v>0.03765666484832764</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0134111987426877</v>
+        <v>0.02711424976587296</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.004125162027776241</v>
+        <v>0.001140212989412248</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0004942591185681522</v>
+        <v>0.06497549265623093</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.005047399550676346</v>
+        <v>0.013987822458148</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001854453585110605</v>
+        <v>0.05000732839107513</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0004624884459190071</v>
+        <v>0.009729556739330292</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.003059763461351395</v>
+        <v>0.01589959487318993</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.003058663103729486</v>
+        <v>0.04420687258243561</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.003492699936032295</v>
+        <v>0.008411002345383167</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.001037397421896458</v>
+        <v>0.0376451313495636</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.006207941565662622</v>
+        <v>0.01438480708748102</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.002722022123634815</v>
+        <v>0.0009874239331111312</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001077980850823224</v>
+        <v>0.03174695372581482</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001298103015869856</v>
+        <v>0.02285423688590527</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.001627403311431408</v>
+        <v>0.04862194135785103</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001095912186428905</v>
+        <v>0.03120045363903046</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.00308299483731389</v>
+        <v>0.0043744295835495</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.003032140899449587</v>
+        <v>0.02297857590019703</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.004386906046420336</v>
+        <v>0.006117802113294601</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.005875102244317532</v>
+        <v>0.007058016955852509</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.002918245038017631</v>
+        <v>0.003114888677373528</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.002307598711922765</v>
+        <v>0.006805957295000553</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.001599618350155652</v>
+        <v>0.08102453500032425</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0007508400012739003</v>
+        <v>0.003328446997329593</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0009585027582943439</v>
+        <v>0.009983403608202934</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.006841313559561968</v>
+        <v>0.05536691844463348</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.003261968493461609</v>
+        <v>0.005169248674064875</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.001991815166547894</v>
+        <v>0.03897669538855553</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004087422508746386</v>
+        <v>0.007182426750659943</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.002522672060877085</v>
+        <v>0.008219819515943527</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001905059791170061</v>
+        <v>0.000448053702712059</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0006648290436714888</v>
+        <v>0.007992547005414963</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001107786665670574</v>
+        <v>0.0120793329551816</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0001643197610974312</v>
+        <v>0.004827917087823153</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.007264981511980295</v>
+        <v>0.02797801792621613</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.006002544891089201</v>
+        <v>0.02593285404145718</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.003806534688919783</v>
+        <v>0.03258576244115829</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.003595478134229779</v>
+        <v>0.01782831735908985</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.007152263075113297</v>
+        <v>0.006074989214539528</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.004648061003535986</v>
+        <v>0.02466970682144165</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.001258953241631389</v>
+        <v>0.01574808172881603</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0002703749923966825</v>
+        <v>0.0552063025534153</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001421970082446933</v>
+        <v>0.02344747819006443</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.01003280002623796</v>
+        <v>0.06406792998313904</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001037554000504315</v>
+        <v>0.01845282688736916</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.004912080708891153</v>
+        <v>0.05443483591079712</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002887103939428926</v>
+        <v>0.003272023517638445</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.002704004989936948</v>
+        <v>0.009439337067306042</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.003019092604517937</v>
+        <v>0.01111341826617718</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001225969521328807</v>
+        <v>0.0228450708091259</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.001862182165496051</v>
+        <v>0.01880311779677868</v>
       </c>
       <c r="FG8" t="n">
-        <v>4.658870602725074e-05</v>
+        <v>0.01356879435479641</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.005487761925905943</v>
+        <v>0.0223630890250206</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001293522771447897</v>
+        <v>0.004508830606937408</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.003139434615150094</v>
+        <v>0.01823367550969124</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.004804532509297132</v>
+        <v>0.01239563245326281</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.001531596062704921</v>
+        <v>0.0109434649348259</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0007788731018081307</v>
+        <v>0.002568863332271576</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0008207870996557176</v>
+        <v>0.003864820348098874</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0004850956611335278</v>
+        <v>0.04651141911745071</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.001138250227086246</v>
+        <v>0.05347573012113571</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.007688293233513832</v>
+        <v>0.04172882065176964</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0102120116353035</v>
+        <v>0.04032342880964279</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.003199113300070167</v>
+        <v>0.06799933314323425</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0004540656227618456</v>
+        <v>0.050979383289814</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.001442506909370422</v>
+        <v>0.01589978858828545</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0005332503351382911</v>
+        <v>0.01478717848658562</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.001321773510426283</v>
+        <v>0.002274934202432632</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.004057745449244976</v>
+        <v>0.001123531488701701</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.005071613937616348</v>
+        <v>0.03178456053137779</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.002419091993942857</v>
+        <v>0.05821990966796875</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.001071598031558096</v>
+        <v>0.01827851496636868</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0008108055917546153</v>
+        <v>0.0604352168738842</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.00906924344599247</v>
+        <v>0.02967390418052673</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.004464901518076658</v>
+        <v>0.02156298980116844</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01149384770542383</v>
+        <v>0.05564911663532257</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0010999416699633</v>
+        <v>0.02989082969725132</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0008422292303293943</v>
+        <v>0.008878298103809357</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.07648757100105286</v>
+        <v>0.007672302890568972</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3926100730895996</v>
+        <v>0.4792012572288513</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01346690766513348</v>
+        <v>0.05757273733615875</v>
       </c>
       <c r="D9" t="n">
-        <v>0.282793790102005</v>
+        <v>0.1144059896469116</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02415131218731403</v>
+        <v>0.01111758127808571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3782631754875183</v>
+        <v>0.4589945673942566</v>
       </c>
       <c r="G9" t="n">
-        <v>7.22445547580719e-05</v>
+        <v>0.07310149073600769</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1585171818733215</v>
+        <v>0.2126860320568085</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03219987824559212</v>
+        <v>0.05322042107582092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1267984658479691</v>
+        <v>0.01512794941663742</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3487373292446136</v>
+        <v>0.6946237087249756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01581966690719128</v>
+        <v>0.02390843629837036</v>
       </c>
       <c r="M9" t="n">
-        <v>0.209324061870575</v>
+        <v>0.1655891835689545</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03307336941361427</v>
+        <v>0.2371734976768494</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4017383456230164</v>
+        <v>0.4665215611457825</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0009293407201766968</v>
+        <v>0.004471523687243462</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04570625349879265</v>
+        <v>0.06036332249641418</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02731857448816299</v>
+        <v>0.1274675875902176</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007683804258704185</v>
+        <v>0.04035741835832596</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03199202194809914</v>
+        <v>0.0738019198179245</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04741742834448814</v>
+        <v>0.07384880632162094</v>
       </c>
       <c r="V9" t="n">
-        <v>0.10029236972332</v>
+        <v>0.08089625090360641</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08705722540616989</v>
+        <v>0.05229842662811279</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0335417278110981</v>
+        <v>0.1244261562824249</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.04190897941589355</v>
+        <v>0.0643441379070282</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0851743295788765</v>
+        <v>0.1948578059673309</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.05595113337039948</v>
+        <v>0.03089902363717556</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01584707200527191</v>
+        <v>0.1301887631416321</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.009042810648679733</v>
+        <v>0.03407399356365204</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01999567821621895</v>
+        <v>0.05470671504735947</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.03857237845659256</v>
+        <v>0.09069083631038666</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.037293940782547</v>
+        <v>0.2305744141340256</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.02229938469827175</v>
+        <v>0.07064065337181091</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.022024255245924</v>
+        <v>0.0425281934440136</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0343199223279953</v>
+        <v>0.252038836479187</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.03757426515221596</v>
+        <v>0.03982216119766235</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.05786124616861343</v>
+        <v>0.02275756374001503</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.06494759768247604</v>
+        <v>0.05545748025178909</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01187702268362045</v>
+        <v>0.0575128085911274</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.03001044318079948</v>
+        <v>0.04835046082735062</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.03363694995641708</v>
+        <v>0.01647331193089485</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.05328125134110451</v>
+        <v>0.03378666192293167</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004012482240796089</v>
+        <v>0.07699629664421082</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.04390633106231689</v>
+        <v>0.2225669175386429</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.05930236726999283</v>
+        <v>0.08783898502588272</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.02332865819334984</v>
+        <v>0.09787243604660034</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2517482936382294</v>
+        <v>0.5589929223060608</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.001247493550181389</v>
+        <v>0.0810900554060936</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.08062747120857239</v>
+        <v>0.02255780436098576</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.01423225365579128</v>
+        <v>0.1855392009019852</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.2027415782213211</v>
+        <v>0.327651172876358</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.009572598151862621</v>
+        <v>0.01345457602292299</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.07239965349435806</v>
+        <v>0.0001983148977160454</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.09402685612440109</v>
+        <v>0.03932824730873108</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.06471153348684311</v>
+        <v>0.07150068134069443</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.08124063163995743</v>
+        <v>0.007269196212291718</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.1074618846178055</v>
+        <v>0.01058933138847351</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.03877118229866028</v>
+        <v>0.09418350458145142</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0647813081741333</v>
+        <v>0.1408199965953827</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.1021450608968735</v>
+        <v>0.01089806109666824</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02517988905310631</v>
+        <v>0.02219649031758308</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.05321663245558739</v>
+        <v>0.09474574774503708</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.03204637765884399</v>
+        <v>0.02674238756299019</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.004111817106604576</v>
+        <v>0.08220469951629639</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.08730306476354599</v>
+        <v>0.1189009100198746</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.03884772583842278</v>
+        <v>0.01019282639026642</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.06117895990610123</v>
+        <v>0.04334986209869385</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01026895642280579</v>
+        <v>0.04938244074583054</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.008740164339542389</v>
+        <v>0.06061966717243195</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01610787771642208</v>
+        <v>0.16108737885952</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003463318571448326</v>
+        <v>0.03008724749088287</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0006116414442658424</v>
+        <v>0.04833222553133965</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01583924144506454</v>
+        <v>9.055435657501221e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1506951451301575</v>
+        <v>0.3288867473602295</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.03934430330991745</v>
+        <v>0.05874433740973473</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.08480056375265121</v>
+        <v>0.1071732416749001</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02623101323843002</v>
+        <v>0.02213205955922604</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.1217393353581429</v>
+        <v>0.1791225522756577</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.03212026879191399</v>
+        <v>0.06746895611286163</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0258847177028656</v>
+        <v>0.09085319191217422</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.06859598308801651</v>
+        <v>0.03656109422445297</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.01139878109097481</v>
+        <v>0.02538710832595825</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.05252899974584579</v>
+        <v>0.1568501144647598</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.05737180635333061</v>
+        <v>0.03454308584332466</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.04217954725027084</v>
+        <v>0.03397439047694206</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.01086455769836903</v>
+        <v>0.01537598576396704</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.06649239361286163</v>
+        <v>0.1189972385764122</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.02907798066735268</v>
+        <v>0.06330671906471252</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.03173980861902237</v>
+        <v>0.01154296565800905</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.04328872263431549</v>
+        <v>0.01191125251352787</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.07655671238899231</v>
+        <v>0.0009464025497436523</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01209830027073622</v>
+        <v>0.2842193841934204</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.01520115789026022</v>
+        <v>0.1045630648732185</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.05478259176015854</v>
+        <v>0.09508925676345825</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01040749438107014</v>
+        <v>0.03428865596652031</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.03093117475509644</v>
+        <v>0.004313373938202858</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0741158202290535</v>
+        <v>0.02664684504270554</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.06919485330581665</v>
+        <v>0.05058646202087402</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.008626976981759071</v>
+        <v>0.02933382615447044</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.002534485887736082</v>
+        <v>0.001830711960792542</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.04660845547914505</v>
+        <v>0.1623360067605972</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.05069323629140854</v>
+        <v>0.007628614082932472</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.06455665826797485</v>
+        <v>0.06019634008407593</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.01729060709476471</v>
+        <v>0.0002492060884833336</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.07559134811162949</v>
+        <v>0.1363631933927536</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.02755830436944962</v>
+        <v>0.03023098595440388</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0539032518863678</v>
+        <v>0.0066639743745327</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.02370550855994225</v>
+        <v>0.01064166892319918</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.006943969056010246</v>
+        <v>0.01421134918928146</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01213866285979748</v>
+        <v>0.07962161302566528</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.03340393677353859</v>
+        <v>0.1077186018228531</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1897188276052475</v>
+        <v>0.04160105064511299</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05734486132860184</v>
+        <v>0.1704093217849731</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0342617854475975</v>
+        <v>0.1226819157600403</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.01191863045096397</v>
+        <v>0.07669426500797272</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.06481108814477921</v>
+        <v>0.04693596810102463</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.03898579254746437</v>
+        <v>0.08370667695999146</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.01560335978865623</v>
+        <v>0.06806827336549759</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.004820507951080799</v>
+        <v>0.1031319350004196</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.02714494802057743</v>
+        <v>0.02527612261474133</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.02153382450342178</v>
+        <v>0.07978236675262451</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0005502135027199984</v>
+        <v>0.05900786444544792</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.01249995455145836</v>
+        <v>0.03756790608167648</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.04097737371921539</v>
+        <v>0.01052294112741947</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.01460038870573044</v>
+        <v>0.1830277591943741</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.07830061763525009</v>
+        <v>0.02802737057209015</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.004957240074872971</v>
+        <v>0.09056199342012405</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.006391254719346762</v>
+        <v>0.07141375541687012</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.05649378150701523</v>
+        <v>0.01437508314847946</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.003391509875655174</v>
+        <v>0.006797589361667633</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.004506848752498627</v>
+        <v>0.04710078984498978</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0443439893424511</v>
+        <v>0.1041188985109329</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.004295150749385357</v>
+        <v>0.055289376527071</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.01173227839171886</v>
+        <v>0.02652626857161522</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.01223699003458023</v>
+        <v>0.08502723276615143</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.02659173868596554</v>
+        <v>0.02964301407337189</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.05579410493373871</v>
+        <v>0.01579218916594982</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.04689610376954079</v>
+        <v>0.02347327210009098</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.009172934107482433</v>
+        <v>0.04368429630994797</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.007239123806357384</v>
+        <v>0.05385638773441315</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0751020759344101</v>
+        <v>0.1156043112277985</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.02874981611967087</v>
+        <v>0.04154980555176735</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.007050494663417339</v>
+        <v>0.03637124598026276</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.01533013489097357</v>
+        <v>0.0152281615883112</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.007805466651916504</v>
+        <v>0.01153212413191795</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.02610275335609913</v>
+        <v>0.03298750519752502</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.05031216517090797</v>
+        <v>0.03167102113366127</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.04176309332251549</v>
+        <v>0.09110648930072784</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.009424624964594841</v>
+        <v>0.05643589422106743</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.02660277672111988</v>
+        <v>0.03771102428436279</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.04472287371754646</v>
+        <v>0.03578599542379379</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.1313193291425705</v>
+        <v>0.024406548589468</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.01745864190161228</v>
+        <v>0.00760801974684</v>
       </c>
       <c r="EX9" t="n">
-        <v>3.949785605072975e-05</v>
+        <v>0.01302377507090569</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.04071930423378944</v>
+        <v>0.1846946328878403</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.04611013829708099</v>
+        <v>0.03072022460401058</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.05674485489726067</v>
+        <v>0.03366655856370926</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01433467864990234</v>
+        <v>0.01744990982115269</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0590803474187851</v>
+        <v>0.1167981401085854</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.04615315049886703</v>
+        <v>0.06138534098863602</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.02969363331794739</v>
+        <v>0.03300606086850166</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.04208364710211754</v>
+        <v>0.005108401644974947</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.02592688053846359</v>
+        <v>0.02511665970087051</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0219959132373333</v>
+        <v>0.1542956680059433</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.03974395245313644</v>
+        <v>0.1016323566436768</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.07368704676628113</v>
+        <v>0.09403130412101746</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01706931181252003</v>
+        <v>0.04561964794993401</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.04532342404127121</v>
+        <v>0.07776202261447906</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.01823220402002335</v>
+        <v>0.06418905407190323</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.03367263078689575</v>
+        <v>0.1989536285400391</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.02038606256246567</v>
+        <v>0.05915509909391403</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.02369365096092224</v>
+        <v>0.08941197395324707</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.04033409804105759</v>
+        <v>0.006711237132549286</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0670081153512001</v>
+        <v>0.1294717788696289</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.04721938818693161</v>
+        <v>0.1309941709041595</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.06228411942720413</v>
+        <v>0.00711417943239212</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01978102512657642</v>
+        <v>0.04496868699789047</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.05001149326562881</v>
+        <v>0.0484093576669693</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0105273611843586</v>
+        <v>0.09327085316181183</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.01611444726586342</v>
+        <v>0.05300753563642502</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0887501984834671</v>
+        <v>0.09049849957227707</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.04535957798361778</v>
+        <v>0.04491881653666496</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0325118750333786</v>
+        <v>0.07058262079954147</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.01488997600972652</v>
+        <v>0.007929028943181038</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.02305366843938828</v>
+        <v>0.1855942606925964</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.03090677410364151</v>
+        <v>0.1241947859525681</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.2497367709875107</v>
+        <v>0.03051277250051498</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.005274198018014431</v>
+        <v>0.09646628797054291</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.05236371606588364</v>
+        <v>0.05603817105293274</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0006636781617999077</v>
+        <v>0.1430472284555435</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1015928834676743</v>
+        <v>0.2433051317930222</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01345747523009777</v>
+        <v>0.0218110978603363</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0079282121732831</v>
+        <v>0.09426923841238022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02120959386229515</v>
+        <v>0.02898460812866688</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01812879182398319</v>
+        <v>0.1287730932235718</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01332996692508459</v>
+        <v>0.04418118670582771</v>
       </c>
       <c r="H10" t="n">
-        <v>9.204231901094317e-05</v>
+        <v>0.06451378017663956</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005829776637256145</v>
+        <v>0.05160913243889809</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01439813151955605</v>
+        <v>0.1131295785307884</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08783640712499619</v>
+        <v>0.3419569134712219</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00624984223395586</v>
+        <v>0.002575799822807312</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01930783689022064</v>
+        <v>0.1412311196327209</v>
       </c>
       <c r="N10" t="n">
-        <v>0.009907284751534462</v>
+        <v>0.05893568322062492</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03766222670674324</v>
+        <v>0.1423945724964142</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01723677292466164</v>
+        <v>0.0223415419459343</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02064021117985249</v>
+        <v>0.06119565665721893</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01087460294365883</v>
+        <v>0.06094324961304665</v>
       </c>
       <c r="S10" t="n">
-        <v>0.007255810312926769</v>
+        <v>0.03233262896537781</v>
       </c>
       <c r="T10" t="n">
-        <v>0.006803846918046474</v>
+        <v>0.05860641226172447</v>
       </c>
       <c r="U10" t="n">
-        <v>0.004276973195374012</v>
+        <v>0.01680050045251846</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001148525741882622</v>
+        <v>0.02815181761980057</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002442880533635616</v>
+        <v>0.03232574835419655</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004205797333270311</v>
+        <v>0.02622781693935394</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.00153111875988543</v>
+        <v>0.02137450873851776</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.02362204529345036</v>
+        <v>0.01506705023348331</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.004862522706389427</v>
+        <v>0.03669813275337219</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.003694597166031599</v>
+        <v>0.05272515118122101</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.00124270492233336</v>
+        <v>0.06290774047374725</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001029811799526215</v>
+        <v>0.02177878841757774</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01277895178645849</v>
+        <v>0.1235110312700272</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00643086526542902</v>
+        <v>0.07849287986755371</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.008439020253717899</v>
+        <v>0.04508732631802559</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.003793420502915978</v>
+        <v>0.006427431479096413</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01003944501280785</v>
+        <v>0.08508791774511337</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001117315026931465</v>
+        <v>0.02789871767163277</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.005108707118779421</v>
+        <v>0.05048065260052681</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.009200754575431347</v>
+        <v>0.004301714710891247</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.003531821072101593</v>
+        <v>0.07352850586175919</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.008774570189416409</v>
+        <v>0.01177317276597023</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.003457643557339907</v>
+        <v>0.03960609436035156</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.15322423982434e-05</v>
+        <v>0.008540048263967037</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.00351420440711081</v>
+        <v>0.01307134982198477</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.002031353767961264</v>
+        <v>0.04842118173837662</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01043660752475262</v>
+        <v>0.02076568454504013</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.02026084437966347</v>
+        <v>0.06917445361614227</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.07371953129768372</v>
+        <v>0.2487532496452332</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.011823452077806</v>
+        <v>0.03919123113155365</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.02402274310588837</v>
+        <v>0.03496014326810837</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.01252482179552317</v>
+        <v>0.1140079349279404</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.01396428048610687</v>
+        <v>0.01355086732655764</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.01115335617214441</v>
+        <v>0.04090817272663116</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.004805280826985836</v>
+        <v>0.02100097388029099</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.002841242589056492</v>
+        <v>0.007564867381006479</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.003364711068570614</v>
+        <v>0.03065034747123718</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.006712272763252258</v>
+        <v>0.06881355494260788</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001912739011459053</v>
+        <v>0.01779627427458763</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001561147160828114</v>
+        <v>0.0333142913877964</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.006533691193908453</v>
+        <v>0.08971759676933289</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01291020680218935</v>
+        <v>0.0698634460568428</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.01244278438389301</v>
+        <v>0.05719130858778954</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01301726046949625</v>
+        <v>0.1072191298007965</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.006949936039745808</v>
+        <v>0.08771376311779022</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.012058868072927</v>
+        <v>0.04105474054813385</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.007019213400781155</v>
+        <v>0.1190416812896729</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001354649662971497</v>
+        <v>0.009513039141893387</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.005300804506987333</v>
+        <v>0.06723713874816895</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.006609998643398285</v>
+        <v>0.07162439823150635</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.02470308355987072</v>
+        <v>0.002097566612064838</v>
       </c>
       <c r="BR10" t="n">
-        <v>2.436712384223938e-05</v>
+        <v>0.09151798486709595</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.02301807329058647</v>
+        <v>0.03789714351296425</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.01855054870247841</v>
+        <v>0.000407293438911438</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01500510796904564</v>
+        <v>0.001709720585495234</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.03802395239472389</v>
+        <v>0.1163035929203033</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.01481173001229763</v>
+        <v>0.007593885064125061</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01061421912163496</v>
+        <v>0.02399404719471931</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.009536707773804665</v>
+        <v>0.03623956069350243</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002083399798721075</v>
+        <v>0.02693474665284157</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0005510407499969006</v>
+        <v>0.02078015543520451</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003221561200916767</v>
+        <v>0.006650618277490139</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.005348841194063425</v>
+        <v>0.0277407243847847</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.00179402600042522</v>
+        <v>0.04240924492478371</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01916370913386345</v>
+        <v>0.04351804777979851</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.009409681893885136</v>
+        <v>0.01351828873157501</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002131748711690307</v>
+        <v>0.03756989538669586</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.00996001623570919</v>
+        <v>0.03611347824335098</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.003025344340130687</v>
+        <v>0.03364968672394753</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.003246016800403595</v>
+        <v>0.007668578997254372</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.003067763987928629</v>
+        <v>0.009567205794155598</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.007982665672898293</v>
+        <v>0.01772451587021351</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.02748009748756886</v>
+        <v>0.04864516854286194</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01500105671584606</v>
+        <v>0.1517738401889801</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.01305042766034603</v>
+        <v>0.03663953021168709</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.02442505210638046</v>
+        <v>0.02199409902095795</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.02166594006121159</v>
+        <v>0.03515481576323509</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.01123540475964546</v>
+        <v>0.02799740619957447</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.02142550982534885</v>
+        <v>0.0123587092384696</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.003843262791633606</v>
+        <v>0.03008837997913361</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.02483048848807812</v>
+        <v>0.07302874326705933</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.002000166568905115</v>
+        <v>0.01809708215296268</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.02156935445964336</v>
+        <v>0.04775285348296165</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.01218452397733927</v>
+        <v>0.02196573093533516</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.006787868682295084</v>
+        <v>0.06569728255271912</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01197709329426289</v>
+        <v>0.003619933966547251</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.006555622909218073</v>
+        <v>0.03835950419306755</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.003688930068165064</v>
+        <v>0.002030942589044571</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.002847854513674974</v>
+        <v>0.003608302213251591</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.006042254623025656</v>
+        <v>0.02082524262368679</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.008104737848043442</v>
+        <v>0.03727496042847633</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.002602576510980725</v>
+        <v>0.05508927255868912</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.002942657331004739</v>
+        <v>0.06713142246007919</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02430740557610989</v>
+        <v>0.004775488283485174</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.003548057284206152</v>
+        <v>0.04286287724971771</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.006893266458064318</v>
+        <v>0.008364763110876083</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01630958169698715</v>
+        <v>0.05519847571849823</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.007632419466972351</v>
+        <v>0.04978986084461212</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.005050638690590858</v>
+        <v>0.007046002428978682</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0009276597993448377</v>
+        <v>0.02958852984011173</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.02228494733572006</v>
+        <v>0.02513472363352776</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.004744996782392263</v>
+        <v>0.002888679504394531</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.002966227009892464</v>
+        <v>0.001471728086471558</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.007141138426959515</v>
+        <v>0.05027424171566963</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.005336820613592863</v>
+        <v>0.05430061742663383</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.002125272527337074</v>
+        <v>0.01755391061306</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.004589803982526064</v>
+        <v>0.02575239539146423</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.01248639170080423</v>
+        <v>0.004240114241838455</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.002243106020614505</v>
+        <v>0.06019988656044006</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01218948699533939</v>
+        <v>0.01665466651320457</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.000681803678162396</v>
+        <v>0.04440897703170776</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001421282067894936</v>
+        <v>0.02294476516544819</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.008278633467853069</v>
+        <v>0.07613110542297363</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.001281690550968051</v>
+        <v>0.03628365322947502</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.004640881903469563</v>
+        <v>0.0006559356115758419</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01727541349828243</v>
+        <v>0.04604740813374519</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0009969114325940609</v>
+        <v>0.05245212838053703</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.009412394836544991</v>
+        <v>0.1344055533409119</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.008794656954705715</v>
+        <v>0.003304639831185341</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.01013097167015076</v>
+        <v>0.006975953467190266</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.002431476023048162</v>
+        <v>0.03388813883066177</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002798676025122404</v>
+        <v>0.01922646164894104</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0007162443362176418</v>
+        <v>0.03935285657644272</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.006477296352386475</v>
+        <v>0.05445685982704163</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.004926808644086123</v>
+        <v>0.004813770763576031</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003608101280406117</v>
+        <v>0.03155623376369476</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.00246690958738327</v>
+        <v>0.0728263258934021</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.01387184578925371</v>
+        <v>0.00847820658236742</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01277011912316084</v>
+        <v>0.05451904237270355</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01556668430566788</v>
+        <v>0.0380282811820507</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01547431666404009</v>
+        <v>0.01036943960934877</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0163373127579689</v>
+        <v>0.0321633480489254</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.008224880322813988</v>
+        <v>0.01812932267785072</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01494089886546135</v>
+        <v>0.001583361881785095</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.005591149907559156</v>
+        <v>0.01061703637242317</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.003071330487728119</v>
+        <v>0.03652853146195412</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01991402357816696</v>
+        <v>0.06857930123806</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.009082963690161705</v>
+        <v>0.02138729207217693</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.002782651921734214</v>
+        <v>0.04867197573184967</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01433609891682863</v>
+        <v>0.007533429190516472</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.005562204867601395</v>
+        <v>0.03862330317497253</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.006955213844776154</v>
+        <v>0.01192276179790497</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.003699518274515867</v>
+        <v>0.008578515611588955</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.008986098691821098</v>
+        <v>0.02081711404025555</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.001942567760124803</v>
+        <v>0.02134266495704651</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.008136087097227573</v>
+        <v>0.06999049335718155</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.002362015657126904</v>
+        <v>0.04055523499846458</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.007998732849955559</v>
+        <v>0.04181206971406937</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.004533004015684128</v>
+        <v>0.1090995296835899</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001095886342227459</v>
+        <v>0.01545446179807186</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.001706009497866035</v>
+        <v>0.01244601234793663</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.00148555135820061</v>
+        <v>0.009453702718019485</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.004734407179057598</v>
+        <v>0.003013471141457558</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01565157994627953</v>
+        <v>0.01123204454779625</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01483951043337584</v>
+        <v>0.01466156914830208</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.00401626992970705</v>
+        <v>0.1239692941308022</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.002916807308793068</v>
+        <v>0.1170033738017082</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.01551987789571285</v>
+        <v>0.1087962687015533</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.01060965098440647</v>
+        <v>0.08674544095993042</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.002498837886378169</v>
+        <v>0.01985269412398338</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.02035862393677235</v>
+        <v>0.01730679161846638</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.008237063884735107</v>
+        <v>0.1395057141780853</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.02096985839307308</v>
+        <v>0.01718958653509617</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.001594717381522059</v>
+        <v>0.002358540892601013</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01345675997436047</v>
+        <v>0.02184632420539856</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.01336744427680969</v>
+        <v>0.008781321346759796</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0204736590385437</v>
+        <v>0.07674863934516907</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02612636797130108</v>
+        <v>0.06583819538354874</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.03178304433822632</v>
+        <v>0.05834358930587769</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.000169677019584924</v>
+        <v>0.02858650870621204</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.000383711711037904</v>
+        <v>0.01550708618015051</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0004725866601802409</v>
+        <v>4.235305823385715e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004236824810504913</v>
+        <v>3.753603596123867e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000607249909080565</v>
+        <v>5.574076567427255e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000925892498344183</v>
+        <v>8.361002983292565e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002410514745861292</v>
+        <v>1.583617404321558e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0005283904611133039</v>
+        <v>1.151005199062638e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001078567351214588</v>
+        <v>1.457371695323673e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002255947183584794</v>
+        <v>3.995132829004433e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0003080040623899549</v>
+        <v>2.948124574686517e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002329405688215047</v>
+        <v>3.559035121725174e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.003723080037161708</v>
+        <v>4.155957867624238e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>9.218493505613878e-05</v>
+        <v>1.081001300917706e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0008635472622700036</v>
+        <v>9.403865988133475e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00150141550693661</v>
+        <v>1.234501178259961e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0006000365247018635</v>
+        <v>4.104896106582601e-06</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001092180260457098</v>
+        <v>3.032221002285951e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0003964815987274051</v>
+        <v>2.419652901153313e-06</v>
       </c>
       <c r="R11" t="n">
-        <v>8.410834561800584e-05</v>
+        <v>1.479833258599683e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0002941048878710717</v>
+        <v>8.889420541891013e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0006716237403452396</v>
+        <v>3.60943431587657e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>5.477475497173145e-06</v>
+        <v>1.04808236756071e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0006816255627200007</v>
+        <v>2.28561202675337e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0002524544834159315</v>
+        <v>4.577864274324384e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0004283628659322858</v>
+        <v>3.624967575888149e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001064929601852782</v>
+        <v>2.942995934063219e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0009754264610819519</v>
+        <v>4.319224899518304e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0004495655011851341</v>
+        <v>2.806555130518973e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0001540796947665513</v>
+        <v>3.114363607892301e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0004412455891724676</v>
+        <v>3.087725417572074e-07</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0002359380887355655</v>
+        <v>1.653430672376999e-07</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0003986382216680795</v>
+        <v>8.514130968251266e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.000882900261785835</v>
+        <v>6.7470898557076e-07</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0004833743441849947</v>
+        <v>7.959768481669016e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0003295313217677176</v>
+        <v>1.648385705266264e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0001593453052919358</v>
+        <v>2.261472218378913e-06</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0002275737060699612</v>
+        <v>6.492636657640105e-06</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0004750519874505699</v>
+        <v>5.980301693853107e-07</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0008194036781787872</v>
+        <v>7.820934115443379e-06</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0002219451125711203</v>
+        <v>4.81890128867235e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.080448782886378e-05</v>
+        <v>2.879823568946449e-06</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.000249636679654941</v>
+        <v>4.753966550197219e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0004385067149996758</v>
+        <v>2.125740820702049e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.172750489786267e-05</v>
+        <v>2.407356532785343e-06</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.940583206305746e-05</v>
+        <v>3.147029701722204e-06</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0003072029794566333</v>
+        <v>9.605455488781445e-07</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0001866990351118147</v>
+        <v>1.206446768264868e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.003378179622814059</v>
+        <v>1.768552829162218e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0005687210941687226</v>
+        <v>2.253918182759662e-06</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.000529659038875252</v>
+        <v>1.227953134730342e-07</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0009951858082786202</v>
+        <v>7.22013601262006e-06</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0002931304625235498</v>
+        <v>7.788466064084787e-06</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0004022042558062822</v>
+        <v>1.488885459366429e-08</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.226508412510157e-05</v>
+        <v>2.718986934269196e-06</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0001504842657595873</v>
+        <v>1.090330101760628e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0001066012628143653</v>
+        <v>4.838563540943142e-07</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0006606959505006671</v>
+        <v>5.918109309277497e-06</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0004891111748293042</v>
+        <v>3.75798867935373e-06</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0003961354668717831</v>
+        <v>5.408428933151299e-06</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.000686373095959425</v>
+        <v>3.589143034332665e-06</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0001269052445422858</v>
+        <v>2.359524842177052e-06</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0010143838590011</v>
+        <v>1.204351633532497e-06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0003283536643721163</v>
+        <v>1.078457103176333e-06</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0002821357047650963</v>
+        <v>3.670383648568531e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.000567795243114233</v>
+        <v>5.681060883944156e-07</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0007824628264643252</v>
+        <v>6.183780897117686e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.036297468701378e-05</v>
+        <v>1.174479393739603e-06</v>
       </c>
       <c r="BO11" t="n">
-        <v>6.164301885291934e-05</v>
+        <v>1.110888661060017e-06</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0003333843196742237</v>
+        <v>5.14185421707225e-06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0005387615528889</v>
+        <v>4.494800123211462e-06</v>
       </c>
       <c r="BR11" t="n">
-        <v>3.817562901531346e-05</v>
+        <v>8.781674978308729e-07</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0001664205628912896</v>
+        <v>1.887456164695323e-06</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0002486083831172436</v>
+        <v>1.502039367551333e-06</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0002984915336128324</v>
+        <v>3.534839834173908e-07</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.002139570191502571</v>
+        <v>1.206839806400239e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.000625397136900574</v>
+        <v>3.948574885725975e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.000130574859213084</v>
+        <v>1.067183461600507e-06</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0002033208147622645</v>
+        <v>6.922569809830748e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0003726656141225249</v>
+        <v>3.921135430573486e-06</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.327106631128117e-05</v>
+        <v>3.298290948805516e-06</v>
       </c>
       <c r="CB11" t="n">
-        <v>7.110922888386995e-05</v>
+        <v>5.800201847705466e-07</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.000285821151919663</v>
+        <v>4.073393711223616e-07</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0001580781827215105</v>
+        <v>2.037437980106915e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0006067585782147944</v>
+        <v>1.191229057440069e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.822231206460856e-05</v>
+        <v>1.200085421260155e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0001275140821235254</v>
+        <v>2.179432158300187e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0002799704379867762</v>
+        <v>4.995487756787043e-07</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0001527192944195122</v>
+        <v>4.588815500028431e-06</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.7606565708993e-05</v>
+        <v>8.892347409528156e-07</v>
       </c>
       <c r="CK11" t="n">
-        <v>3.54203766619321e-05</v>
+        <v>1.934435658768052e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0001829858520068228</v>
+        <v>6.604752798011759e-07</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0007435167208313942</v>
+        <v>7.363672693827539e-08</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.000871279276907444</v>
+        <v>8.136913493217435e-06</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001554172049509361</v>
+        <v>6.84310907672625e-06</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0004617464146576822</v>
+        <v>1.223072558786953e-07</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001309681916609406</v>
+        <v>3.283372961959685e-06</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.000317972298944369</v>
+        <v>5.035758476878982e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0004479833005461842</v>
+        <v>5.40364317203057e-06</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0001234996307175606</v>
+        <v>3.398208264115965e-06</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54843528434867e-05</v>
+        <v>2.675999894563574e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>6.748511805199087e-05</v>
+        <v>1.259591726920917e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0005286522791720927</v>
+        <v>1.167054324469063e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>6.519890303025022e-05</v>
+        <v>1.694556203801767e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0003066554199904203</v>
+        <v>2.007269813475432e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0001957818458322436</v>
+        <v>9.194845347337832e-07</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0003462890454102308</v>
+        <v>4.922617790725781e-06</v>
       </c>
       <c r="DB11" t="n">
-        <v>4.219957918394357e-05</v>
+        <v>1.996672608584049e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.136267175956164e-05</v>
+        <v>1.274239707527158e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.074094274779782e-05</v>
+        <v>4.449712207588163e-07</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0002091337810270488</v>
+        <v>2.871430297091138e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>5.411971505964175e-05</v>
+        <v>7.561618986073881e-06</v>
       </c>
       <c r="DG11" t="n">
-        <v>4.067560803378001e-05</v>
+        <v>2.214759206253802e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.001440971624106169</v>
+        <v>8.735044048080454e-07</v>
       </c>
       <c r="DI11" t="n">
-        <v>1.124323534895666e-05</v>
+        <v>6.073180429666536e-06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0003129861142951995</v>
+        <v>1.373430313833524e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0004587142029777169</v>
+        <v>4.702039859694196e-07</v>
       </c>
       <c r="DL11" t="n">
-        <v>1.478975354984868e-05</v>
+        <v>2.802581548166927e-06</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.73134410235798e-05</v>
+        <v>1.397152686877234e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0005005663260817528</v>
+        <v>5.417567763288389e-07</v>
       </c>
       <c r="DO11" t="n">
-        <v>5.228644295129925e-05</v>
+        <v>4.716911462310236e-06</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0003377205575816333</v>
+        <v>3.619300514401402e-06</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.399189881747589e-05</v>
+        <v>5.263481853035046e-06</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0002511228376533836</v>
+        <v>1.957376525751897e-06</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0004374716663733125</v>
+        <v>1.579556396791304e-07</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0001240244309883565</v>
+        <v>4.285195700504119e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0002539941342547536</v>
+        <v>2.048267333520926e-06</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0003377941902726889</v>
+        <v>5.348250851966441e-06</v>
       </c>
       <c r="DW11" t="n">
-        <v>3.700199886225164e-05</v>
+        <v>7.176585086199339e-07</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0001254926901310682</v>
+        <v>1.740536390570924e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.000235678133321926</v>
+        <v>6.081226047172095e-07</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0002833318721968681</v>
+        <v>8.453084774373565e-07</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0004443447396624833</v>
+        <v>2.080396143355756e-06</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.000216114945942536</v>
+        <v>5.548006356548285e-06</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0001014934605336748</v>
+        <v>4.518595062563691e-07</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0001188200403703377</v>
+        <v>8.516815796610899e-06</v>
       </c>
       <c r="EE11" t="n">
-        <v>3.686336276587099e-05</v>
+        <v>3.919683877029456e-06</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.000152308537508361</v>
+        <v>2.971666845041909e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0008684570202603936</v>
+        <v>9.146797310677357e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0001452759606763721</v>
+        <v>1.014423560263822e-06</v>
       </c>
       <c r="EI11" t="n">
-        <v>8.280496695078909e-05</v>
+        <v>1.984955702027946e-07</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0008723969804123044</v>
+        <v>2.542947640904458e-06</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0002934967051260173</v>
+        <v>4.778058155352483e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>5.54282269149553e-05</v>
+        <v>2.670492676770664e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0001761719904607162</v>
+        <v>1.823362254071981e-06</v>
       </c>
       <c r="EN11" t="n">
-        <v>4.842071575694717e-05</v>
+        <v>9.066467043794546e-08</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0002614149416331202</v>
+        <v>1.314838982580113e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>8.831179729895666e-05</v>
+        <v>1.087312921299599e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0005006648134440184</v>
+        <v>6.948801001271931e-07</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0003819148114416748</v>
+        <v>1.860632778516447e-06</v>
       </c>
       <c r="ES11" t="n">
-        <v>4.562132744467817e-06</v>
+        <v>2.804182713589398e-06</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0007155184866860509</v>
+        <v>1.945334560105039e-07</v>
       </c>
       <c r="EU11" t="n">
-        <v>3.980855399277061e-05</v>
+        <v>1.018038460642856e-06</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0006156246527098119</v>
+        <v>1.180829940494732e-06</v>
       </c>
       <c r="EW11" t="n">
-        <v>2.069785659841727e-05</v>
+        <v>5.596183427769574e-07</v>
       </c>
       <c r="EX11" t="n">
-        <v>5.685737050953321e-05</v>
+        <v>2.386238065810176e-06</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.000514483661390841</v>
+        <v>1.271597193408525e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>8.498623174091335e-06</v>
+        <v>1.210451841870963e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0002277157327625901</v>
+        <v>1.78814377704839e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>9.050985681824386e-05</v>
+        <v>8.835411904328794e-07</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0002310510317329317</v>
+        <v>4.226645160088083e-06</v>
       </c>
       <c r="FD11" t="n">
-        <v>9.828702604863793e-05</v>
+        <v>1.306465492234565e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>6.180303898872808e-05</v>
+        <v>8.205994390664273e-07</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0001718245766824111</v>
+        <v>1.279085950045555e-06</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0001057755289366469</v>
+        <v>6.978918918321142e-07</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0004063581000082195</v>
+        <v>5.113085080665769e-06</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0003916023706551641</v>
+        <v>1.376252043883142e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0002563680172897875</v>
+        <v>2.953783450720948e-06</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0002533768711145967</v>
+        <v>4.307999859065603e-07</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0002319576597074047</v>
+        <v>3.998647571279434e-06</v>
       </c>
       <c r="FM11" t="n">
-        <v>4.695988172898069e-05</v>
+        <v>8.316093271787395e-07</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0005167444469407201</v>
+        <v>5.276464435155503e-06</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0002405894047114998</v>
+        <v>2.612115849842667e-06</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0002001738757826388</v>
+        <v>2.040959770965856e-06</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0004666943568736315</v>
+        <v>5.58960209673387e-07</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0004827422380913049</v>
+        <v>4.306268692744197e-06</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.001007784740068018</v>
+        <v>5.902473276364617e-06</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0006423215963877738</v>
+        <v>1.760634063430189e-06</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.000337824400048703</v>
+        <v>2.85896066998248e-06</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0005202520405873656</v>
+        <v>1.883194272522815e-06</v>
       </c>
       <c r="FW11" t="n">
-        <v>4.095653639524244e-05</v>
+        <v>8.541765964764636e-06</v>
       </c>
       <c r="FX11" t="n">
-        <v>3.234428004361689e-05</v>
+        <v>7.543892934336327e-06</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.000658562290482223</v>
+        <v>4.333222022978589e-06</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0002925050794146955</v>
+        <v>6.48766854283167e-06</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0001242925645783544</v>
+        <v>7.212341301965353e-07</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0004670117923524231</v>
+        <v>2.296634420417831e-07</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0004736269183922559</v>
+        <v>1.054843892234203e-06</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0005468977033160627</v>
+        <v>4.021206223114859e-06</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.00143713119905442</v>
+        <v>3.265083705628058e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>5.546771717490628e-05</v>
+        <v>1.513409529252385e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0001925962424138561</v>
+        <v>2.72894840236404e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0001332366664428264</v>
+        <v>3.417581950770909e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004255260340869427</v>
+        <v>3.006866506893857e-07</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002422862220555544</v>
+        <v>1.072472457508411e-07</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001942409726325423</v>
+        <v>3.025217552021786e-07</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0003303326084278524</v>
+        <v>3.199324396518932e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0003602947399485856</v>
+        <v>2.181389930910882e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0006738613592460752</v>
+        <v>2.450390752528619e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002279365435242653</v>
+        <v>1.609719788575603e-07</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0005578308482654393</v>
+        <v>6.341998926018277e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0009122660267166793</v>
+        <v>3.980739649023235e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003432069672271609</v>
+        <v>4.110420945835358e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001736092497594655</v>
+        <v>1.413156525131853e-07</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0008591493242420256</v>
+        <v>3.785552564750105e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0009026364423334599</v>
+        <v>3.456651427313773e-07</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003159661137033254</v>
+        <v>2.092978661494271e-07</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0005506781162694097</v>
+        <v>1.532464182218973e-07</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0003478184225969017</v>
+        <v>1.004851881702962e-07</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002663539198692888</v>
+        <v>3.653320135299509e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003992111305706203</v>
+        <v>9.41092181960812e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0003519670572131872</v>
+        <v>2.833698786730565e-08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.202541847713292e-06</v>
+        <v>6.459251267187938e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0004428097163327038</v>
+        <v>6.022080611955971e-08</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0005850224988535047</v>
+        <v>9.961483016240891e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0005140627035871148</v>
+        <v>9.870910133713551e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.000148627907037735</v>
+        <v>2.320200565009145e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0005972477374598384</v>
+        <v>1.642959368552965e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0004740126023534685</v>
+        <v>7.395745171834278e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0003100515459664166</v>
+        <v>7.260296541744538e-08</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.001314241206273437</v>
+        <v>1.296429985586656e-07</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.815193900256418e-05</v>
+        <v>4.897268723880188e-08</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0001444525696570054</v>
+        <v>8.17787650930768e-08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.000478805013699457</v>
+        <v>9.678474022223327e-09</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0003846973995678127</v>
+        <v>6.582548195410709e-08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0002144172613043338</v>
+        <v>2.068556526069187e-08</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0002039381506619975</v>
+        <v>1.855501352565625e-07</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0001139064697781578</v>
+        <v>5.554187865186577e-08</v>
       </c>
       <c r="AK12" t="n">
-        <v>6.301509711192921e-05</v>
+        <v>1.351899925339239e-08</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0004959793877787888</v>
+        <v>4.835821965087916e-09</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0005637645372189581</v>
+        <v>1.282309511907442e-07</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0001421297347405925</v>
+        <v>5.814623449396095e-08</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001466371031710878</v>
+        <v>9.851324023202324e-08</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0006947169313207269</v>
+        <v>1.053185343380392e-07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001116874918807298</v>
+        <v>1.028777596445707e-08</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0001570856693433598</v>
+        <v>8.63739728629298e-08</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0004861437191721052</v>
+        <v>1.750391120936001e-08</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.00013276758545544</v>
+        <v>9.176174486924538e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.002329339506104589</v>
+        <v>4.149957248955616e-07</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001056704670190811</v>
+        <v>5.060280017232799e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0009799961699172854</v>
+        <v>1.32943682729092e-07</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0008201063028536737</v>
+        <v>2.389402027347387e-07</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0004541056405287236</v>
+        <v>3.540167980986553e-08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0002640017191879451</v>
+        <v>1.978446917405563e-08</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.346061127260327e-05</v>
+        <v>6.071871183621624e-08</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0004542285460047424</v>
+        <v>4.445105616923684e-08</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0001158081431640312</v>
+        <v>5.209953002349721e-08</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.001508282031863928</v>
+        <v>3.304157303318789e-08</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.001085905358195305</v>
+        <v>1.18217528211062e-07</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0004345017659943551</v>
+        <v>1.421365158904564e-08</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.001240079407580197</v>
+        <v>2.994467251937749e-08</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0002076868404401466</v>
+        <v>6.992581802478526e-08</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0002853831392712891</v>
+        <v>6.818221010007619e-08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0006569893448613584</v>
+        <v>1.373267082271923e-07</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0004999522934667766</v>
+        <v>2.365929674397194e-11</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0003995106962975115</v>
+        <v>1.623703305142499e-08</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.000726044992916286</v>
+        <v>1.91967743035093e-07</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0007557735661976039</v>
+        <v>7.591327744194132e-08</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0002196195418946445</v>
+        <v>8.809891482997045e-08</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0004854427825193852</v>
+        <v>1.858502685081476e-07</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0005305347731336951</v>
+        <v>4.753719196060047e-08</v>
       </c>
       <c r="BR12" t="n">
-        <v>2.231745020253584e-05</v>
+        <v>2.23652136810415e-07</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0003269662847742438</v>
+        <v>5.795186908130745e-08</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0003962299088016152</v>
+        <v>7.062217122211223e-08</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.000253054837230593</v>
+        <v>4.899979799688481e-08</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.001011422835290432</v>
+        <v>2.276246107157931e-07</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.001397194340825081</v>
+        <v>3.33024168241991e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0001965900446521118</v>
+        <v>9.360915242950796e-08</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0006499954615719616</v>
+        <v>1.245824989837274e-07</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.000205574237043038</v>
+        <v>3.398218595407343e-08</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0001291757653234527</v>
+        <v>8.50618846470752e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0002141079748980701</v>
+        <v>2.784040198378079e-08</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.382072413340211e-05</v>
+        <v>8.399730688779528e-08</v>
       </c>
       <c r="CD12" t="n">
-        <v>6.839036359451711e-06</v>
+        <v>3.582409036084755e-09</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0008790022111497819</v>
+        <v>8.58815596416207e-08</v>
       </c>
       <c r="CF12" t="n">
-        <v>5.319055344443768e-05</v>
+        <v>3.332988107729307e-09</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0001059043861459941</v>
+        <v>1.056179712577432e-07</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0002643539046403021</v>
+        <v>7.023589176924361e-08</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.933182622655295e-05</v>
+        <v>5.616547227305091e-08</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.623240187764168e-05</v>
+        <v>6.520910744711728e-08</v>
       </c>
       <c r="CK12" t="n">
-        <v>2.134828537236899e-05</v>
+        <v>1.684737860330188e-08</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0001151030446635559</v>
+        <v>2.061080905946255e-08</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0006643117521889508</v>
+        <v>1.816649870534093e-07</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0006045287591405213</v>
+        <v>3.142443176784582e-07</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0001740322913974524</v>
+        <v>3.305255447116906e-08</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0003751100739464164</v>
+        <v>1.167420862202562e-07</v>
       </c>
       <c r="CQ12" t="n">
-        <v>7.811632531229407e-05</v>
+        <v>1.411349046520627e-07</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0006318620871752501</v>
+        <v>2.207812599408498e-09</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0006744491402059793</v>
+        <v>4.498587813372978e-08</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0003175800084136426</v>
+        <v>1.915234548732769e-08</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0004445761442184448</v>
+        <v>1.084458478572969e-08</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.896397199947387e-05</v>
+        <v>2.177959146365538e-08</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.000773188192397356</v>
+        <v>8.7151398986407e-08</v>
       </c>
       <c r="CX12" t="n">
-        <v>8.839303336571902e-05</v>
+        <v>1.262640125787584e-08</v>
       </c>
       <c r="CY12" t="n">
-        <v>9.520324965706095e-05</v>
+        <v>1.37093849161829e-07</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0004683922161348164</v>
+        <v>3.033601814195208e-08</v>
       </c>
       <c r="DA12" t="n">
-        <v>5.976080865366384e-05</v>
+        <v>6.474613201135071e-08</v>
       </c>
       <c r="DB12" t="n">
-        <v>2.661976395756938e-05</v>
+        <v>3.700110795534783e-08</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0001021787174977362</v>
+        <v>4.20911661080936e-09</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.000253668986260891</v>
+        <v>2.627341899597013e-08</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0006627558614127338</v>
+        <v>1.849437403222964e-08</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0007975596818141639</v>
+        <v>2.743791860382316e-10</v>
       </c>
       <c r="DG12" t="n">
-        <v>8.541649731341749e-05</v>
+        <v>2.766771878270902e-08</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0002054179785773158</v>
+        <v>6.999727020229329e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0004945924738422036</v>
+        <v>8.979704801959087e-08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0009659149218350649</v>
+        <v>3.143675542105484e-08</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0007817810983397067</v>
+        <v>8.772005344326317e-11</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0003118887834716588</v>
+        <v>4.923455065863891e-08</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0002418670919723809</v>
+        <v>2.049672431780891e-08</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0003152443678118289</v>
+        <v>5.347439824276989e-08</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0003014901594724506</v>
+        <v>3.013627747350256e-08</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.000282328313915059</v>
+        <v>1.198676802260934e-08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0001513121096650138</v>
+        <v>7.039616889414901e-08</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0001711116929072887</v>
+        <v>2.897373541088655e-08</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0005053661298006773</v>
+        <v>6.841244015731718e-08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0004265407333150506</v>
+        <v>1.620321654627332e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0004177838272880763</v>
+        <v>5.735923735983306e-08</v>
       </c>
       <c r="DV12" t="n">
-        <v>1.595854701008648e-05</v>
+        <v>3.471607712413061e-08</v>
       </c>
       <c r="DW12" t="n">
-        <v>2.049755130428821e-05</v>
+        <v>4.040119350179339e-08</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.000993185443803668</v>
+        <v>1.501178381602131e-08</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.291579095181078e-06</v>
+        <v>7.73318191704675e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.726910704746842e-05</v>
+        <v>9.443422754884523e-08</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0001205053049488924</v>
+        <v>6.603829927342986e-09</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0002344702952541411</v>
+        <v>4.792979169110367e-08</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0002798395289573818</v>
+        <v>8.030971088146543e-08</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0001598845701664686</v>
+        <v>2.675913179928102e-08</v>
       </c>
       <c r="EE12" t="n">
-        <v>9.242765372619033e-05</v>
+        <v>1.11272537850482e-08</v>
       </c>
       <c r="EF12" t="n">
-        <v>6.890779332024977e-05</v>
+        <v>2.456593328759027e-08</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0002957367978524417</v>
+        <v>5.14132381113086e-09</v>
       </c>
       <c r="EH12" t="n">
-        <v>6.334336649160832e-05</v>
+        <v>4.154268040679199e-08</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0003343357529956847</v>
+        <v>9.516421783928308e-08</v>
       </c>
       <c r="EJ12" t="n">
-        <v>7.391301187453791e-05</v>
+        <v>1.437265773063245e-08</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.000450068706413731</v>
+        <v>7.208025465388346e-08</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0001458292244933546</v>
+        <v>3.807721782322915e-08</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.246550164069049e-05</v>
+        <v>4.746563675439575e-08</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0001879387709777802</v>
+        <v>1.590915488236533e-08</v>
       </c>
       <c r="EO12" t="n">
-        <v>3.049638326046988e-05</v>
+        <v>4.707943901394174e-08</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0007767134229652584</v>
+        <v>4.522081553659518e-08</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0003681314992718399</v>
+        <v>4.167020506429253e-08</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.000267237366642803</v>
+        <v>3.273235904543981e-08</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0006588277174159884</v>
+        <v>6.318574463648474e-08</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0003066356584895402</v>
+        <v>2.769583673511988e-08</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0003421793808229268</v>
+        <v>4.715748858075131e-08</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0008248658268712461</v>
+        <v>1.581878272816084e-08</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0007913424051366746</v>
+        <v>3.419757632627807e-08</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0001200207479996607</v>
+        <v>2.040705915362651e-08</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0008353039738722146</v>
+        <v>9.677584955625207e-08</v>
       </c>
       <c r="EZ12" t="n">
-        <v>1.908768899738789e-05</v>
+        <v>5.452684526119356e-09</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0001402481575496495</v>
+        <v>1.266386107090511e-07</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0003236796474084258</v>
+        <v>3.488470667889487e-08</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.000145750236697495</v>
+        <v>6.377099026622091e-08</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001167779628303833</v>
+        <v>7.312262084724352e-08</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0002895595098379999</v>
+        <v>3.734091080787039e-08</v>
       </c>
       <c r="FF12" t="n">
-        <v>4.440094926394522e-05</v>
+        <v>1.835986473963658e-08</v>
       </c>
       <c r="FG12" t="n">
-        <v>3.380846465006471e-06</v>
+        <v>2.93791817540523e-08</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0003410190402064472</v>
+        <v>8.034518828026194e-08</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.000267653027549386</v>
+        <v>1.248469949644004e-08</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0004620289255399257</v>
+        <v>1.704618171061156e-07</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0007401605253107846</v>
+        <v>1.564121809849439e-08</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0003615549067035317</v>
+        <v>1.767682000775039e-08</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0002034816861851141</v>
+        <v>3.832177242202306e-08</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.000112411318696104</v>
+        <v>5.267314406864898e-08</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0007596545619890094</v>
+        <v>7.80426958613134e-08</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0001604486897122115</v>
+        <v>6.042693456720372e-08</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0001729434734443203</v>
+        <v>7.938068868895698e-09</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0007318134885281324</v>
+        <v>2.487496963965441e-08</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0006715023773722351</v>
+        <v>1.238909703715763e-07</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0008054838981479406</v>
+        <v>1.399407665303443e-07</v>
       </c>
       <c r="FU12" t="n">
-        <v>2.426819992251694e-05</v>
+        <v>2.578150670728974e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0002250585530418903</v>
+        <v>2.639444396379531e-08</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.000117223353299778</v>
+        <v>8.193694611691171e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>5.542821600101888e-05</v>
+        <v>1.726957599146317e-08</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0002634321863297373</v>
+        <v>2.983755820196166e-08</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0002108885673806071</v>
+        <v>2.120700282048915e-09</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0003165356465615332</v>
+        <v>1.147917938482124e-08</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0007354354602284729</v>
+        <v>2.258139630839651e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0003672642633318901</v>
+        <v>6.539745811551256e-08</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0006644271197728813</v>
+        <v>9.72850173752704e-08</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.000326176144881174</v>
+        <v>1.828841504902812e-07</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.001851564738899469</v>
+        <v>7.740131025002484e-08</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0001260879944311455</v>
+        <v>2.410075339298601e-08</v>
       </c>
     </row>
     <row r="13">
@@ -8396,571 +8396,571 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0003309521707706153</v>
+        <v>0.08958915621042252</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01020889822393656</v>
+        <v>0.2093977779150009</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004933688323944807</v>
+        <v>0.01843085139989853</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002345356857404113</v>
+        <v>0.1091515943408012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002743534976616502</v>
+        <v>0.1003872156143188</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001463341293856502</v>
+        <v>0.1830097585916519</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0008470211178064346</v>
+        <v>0.1554904282093048</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001355320098809898</v>
+        <v>0.1736185848712921</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0002496523084118962</v>
+        <v>0.03421635553240776</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001324812066741288</v>
+        <v>0.04931644350290298</v>
       </c>
       <c r="K15" t="n">
-        <v>0.008335326798260212</v>
+        <v>0.2346750348806381</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002135782851837575</v>
+        <v>0.09202630817890167</v>
       </c>
       <c r="M15" t="n">
-        <v>0.002121752128005028</v>
+        <v>0.1565651744604111</v>
       </c>
       <c r="N15" t="n">
-        <v>0.002376151038333774</v>
+        <v>0.09983111917972565</v>
       </c>
       <c r="O15" t="n">
-        <v>0.002000309759750962</v>
+        <v>0.1777734756469727</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0008401586092077196</v>
+        <v>0.1598551571369171</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0005192842800170183</v>
+        <v>0.05646371468901634</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004292428493499756</v>
+        <v>0.02494188398122787</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0005248190136626363</v>
+        <v>0.02769318595528603</v>
       </c>
       <c r="T15" t="n">
-        <v>0.001324471551924944</v>
+        <v>0.009330753237009048</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0002184947661589831</v>
+        <v>0.05256989598274231</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0003149616532027721</v>
+        <v>0.04274038225412369</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0005149458884261549</v>
+        <v>0.06718306243419647</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0009886050829663873</v>
+        <v>0.03395970165729523</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0005164660979062319</v>
+        <v>0.04184659942984581</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.001565232290886343</v>
+        <v>0.02267587184906006</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0008410577429458499</v>
+        <v>0.04337981715798378</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.348033927381039e-06</v>
+        <v>0.01165240630507469</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.001174053410068154</v>
+        <v>0.06935912370681763</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.724517930299044e-05</v>
+        <v>0.008500013500452042</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0001801004400476813</v>
+        <v>0.09792141616344452</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0006772180204279721</v>
+        <v>0.1950393170118332</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001255914568901062</v>
+        <v>0.04314684122800827</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.522080856375396e-05</v>
+        <v>0.02839631028473377</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0005901202093809843</v>
+        <v>0.1511600017547607</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0005323300138115883</v>
+        <v>0.02910124883055687</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0008733859285712242</v>
+        <v>0.02971479669213295</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.00124682835303247</v>
+        <v>0.03357080742716789</v>
       </c>
       <c r="AM15" t="n">
-        <v>4.56220586784184e-05</v>
+        <v>0.111667163670063</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0001810917747206986</v>
+        <v>0.00535809900611639</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0008285320946015418</v>
+        <v>0.1430162191390991</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.000784116389695555</v>
+        <v>0.02513299137353897</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0001656899694353342</v>
+        <v>0.02670318447053432</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0006073180702514946</v>
+        <v>0.03609852120280266</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0005517704412341118</v>
+        <v>0.004753530956804752</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0004180134274065495</v>
+        <v>0.02380065992474556</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.006224182434380054</v>
+        <v>0.2861977815628052</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.001060449983924627</v>
+        <v>0.08309423923492432</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0002506057207938284</v>
+        <v>0.06074333935976028</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0001925923861563206</v>
+        <v>0.2027795910835266</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0002708454849198461</v>
+        <v>0.1174091622233391</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0003683898830786347</v>
+        <v>0.0371943898499012</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.001075163600035012</v>
+        <v>0.00604584813117981</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0003802600258495659</v>
+        <v>0.04742186516523361</v>
       </c>
       <c r="BC15" t="n">
-        <v>9.454402606934309e-05</v>
+        <v>0.0094914510846138</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.002358595840632915</v>
+        <v>0.09639209508895874</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.00169995310716331</v>
+        <v>0.02805356867611408</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.026107490062714e-06</v>
+        <v>0.035493403673172</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.001071799895726144</v>
+        <v>0.1218670532107353</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0003629990096669644</v>
+        <v>0.002444174140691757</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0002560206921771169</v>
+        <v>0.04595902189612389</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0001996267674257979</v>
+        <v>0.1742491126060486</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0002121634315699339</v>
+        <v>0.03054756298661232</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0003346144803799689</v>
+        <v>0.02065842412412167</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.001302135176956654</v>
+        <v>0.2536347806453705</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.00097162916790694</v>
+        <v>0.04253318905830383</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0003823006991297007</v>
+        <v>0.00743490643799305</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0008100557024590671</v>
+        <v>0.1063997447490692</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0009075912530533969</v>
+        <v>0.002696839394047856</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.000349478330463171</v>
+        <v>0.1513941138982773</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.0009827791946008801</v>
+        <v>0.02941365726292133</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.001106306910514832</v>
+        <v>0.01202849578112364</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.0004182223347015679</v>
+        <v>0.01317125093191862</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.003813008079305291</v>
+        <v>0.09388256818056107</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.001131922705098987</v>
+        <v>0.03816870599985123</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0005213548429310322</v>
+        <v>0.04997005313634872</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.062587671185611e-05</v>
+        <v>0.05145630985498428</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0005316293681971729</v>
+        <v>0.06238521635532379</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0003949552483391017</v>
+        <v>0.05995920673012733</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0002700207987800241</v>
+        <v>0.009488077834248543</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0008200928568840027</v>
+        <v>0.007098369300365448</v>
       </c>
       <c r="CD15" t="n">
-        <v>1.391505065839738e-05</v>
+        <v>0.02172231301665306</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.001601623138412833</v>
+        <v>0.02145831286907196</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0005527001339942217</v>
+        <v>0.009288432076573372</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.000505299714859575</v>
+        <v>0.02072748914361</v>
       </c>
       <c r="CH15" t="n">
-        <v>6.8920839112252e-05</v>
+        <v>0.04290742799639702</v>
       </c>
       <c r="CI15" t="n">
-        <v>7.825018838047981e-05</v>
+        <v>0.05375892296433449</v>
       </c>
       <c r="CJ15" t="n">
-        <v>8.766233804635704e-05</v>
+        <v>0.03008155524730682</v>
       </c>
       <c r="CK15" t="n">
-        <v>8.077686652541161e-05</v>
+        <v>0.02947379276156425</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.000660878315102309</v>
+        <v>0.01296221651136875</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.001397021929733455</v>
+        <v>0.08997951447963715</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0009219925268553197</v>
+        <v>0.2101251035928726</v>
       </c>
       <c r="CO15" t="n">
-        <v>4.521656956057996e-05</v>
+        <v>0.04526376351714134</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0008834340842440724</v>
+        <v>0.07528190314769745</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.003030634252354503</v>
+        <v>0.09395412355661392</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.001326374593190849</v>
+        <v>0.0129909161478281</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0013459442416206</v>
+        <v>0.08788836002349854</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0004907124675810337</v>
+        <v>0.1034955382347107</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0004266399482730776</v>
+        <v>0.03563802689313889</v>
       </c>
       <c r="CV15" t="n">
-        <v>7.368363003479317e-05</v>
+        <v>0.006512612104415894</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.001517687109299004</v>
+        <v>0.02282845228910446</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.0007175677455961704</v>
+        <v>0.006414225324988365</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0008200556039810181</v>
+        <v>0.04521640762686729</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0002199160517193377</v>
+        <v>0.009263975545763969</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.000320090854074806</v>
+        <v>0.06618410348892212</v>
       </c>
       <c r="DB15" t="n">
-        <v>4.967927816323936e-05</v>
+        <v>0.0238870345056057</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.093204991775565e-05</v>
+        <v>0.02979742921888828</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0004245764284860343</v>
+        <v>0.005967619363218546</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0007458759355358779</v>
+        <v>0.0602433830499649</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.002112132497131824</v>
+        <v>0.04303312301635742</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0003979857137892395</v>
+        <v>0.01985040307044983</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.002850380260497332</v>
+        <v>0.009051005356013775</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.001120635424740613</v>
+        <v>0.003298232331871986</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0004922777297906578</v>
+        <v>0.1396473944187164</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.0008133662049658597</v>
+        <v>0.01092847343534231</v>
       </c>
       <c r="DL15" t="n">
-        <v>8.327526302309707e-06</v>
+        <v>0.08256814628839493</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0001937842171173543</v>
+        <v>0.05029848217964172</v>
       </c>
       <c r="DN15" t="n">
-        <v>8.571468060836196e-05</v>
+        <v>0.04913623631000519</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0008067404851317406</v>
+        <v>0.02766982652246952</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.0004883728688582778</v>
+        <v>0.03955936804413795</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0005851501482538879</v>
+        <v>0.06640610843896866</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0002619476872496307</v>
+        <v>0.06614740192890167</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0001862327335402369</v>
+        <v>0.03464449197053909</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.0001554985938128084</v>
+        <v>0.004217399284243584</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0003766729205381125</v>
+        <v>0.05799636617302895</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.0007519510691054165</v>
+        <v>0.01722957566380501</v>
       </c>
       <c r="DW15" t="n">
-        <v>6.132306589279324e-05</v>
+        <v>0.045109573751688</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.001237064250744879</v>
+        <v>0.01781266927719116</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.0002863752888515592</v>
+        <v>0.00145321898162365</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0001036806497722864</v>
+        <v>0.06076964735984802</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.001040827017277479</v>
+        <v>0.06105246394872665</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.000614413118455559</v>
+        <v>0.03850046917796135</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0004576759820338339</v>
+        <v>0.04268727824091911</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0001406334486091509</v>
+        <v>0.07928323000669479</v>
       </c>
       <c r="EE15" t="n">
-        <v>6.113057679613121e-06</v>
+        <v>0.02363862097263336</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0004967957502231002</v>
+        <v>0.009875284507870674</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.001510525005869567</v>
+        <v>0.06454151123762131</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0006200372008606791</v>
+        <v>0.009401783347129822</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0004755855770781636</v>
+        <v>0.03675125539302826</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0007279801066033542</v>
+        <v>0.001522271777503192</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0004464377998374403</v>
+        <v>0.03204109519720078</v>
       </c>
       <c r="EL15" t="n">
-        <v>9.331382170785218e-05</v>
+        <v>0.02929207496345043</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0005390823353081942</v>
+        <v>0.002737692557275295</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0003518866433296353</v>
+        <v>0.002628547605127096</v>
       </c>
       <c r="EO15" t="n">
-        <v>7.491055293940008e-05</v>
+        <v>0.05080868303775787</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0007156076608225703</v>
+        <v>0.020024374127388</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.001065024291165173</v>
+        <v>0.03844152390956879</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.001208738889545202</v>
+        <v>0.006263196934014559</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.001147657982073724</v>
+        <v>0.03449069708585739</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0007962871459312737</v>
+        <v>0.01792409271001816</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.0006871604127809405</v>
+        <v>0.01943578198552132</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.0009961114265024662</v>
+        <v>0.01875334791839123</v>
       </c>
       <c r="EW15" t="n">
-        <v>9.971144027076662e-05</v>
+        <v>0.0677681565284729</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0001731602242216468</v>
+        <v>0.006639841012656689</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.001622683485038579</v>
+        <v>0.05603913962841034</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0004758003342431039</v>
+        <v>0.009265175089240074</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0006721583777107298</v>
+        <v>0.02841280028223991</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0003662090748548508</v>
+        <v>0.003308048471808434</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.000339439429808408</v>
+        <v>0.05555813387036324</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0004130709276068956</v>
+        <v>0.03510696440935135</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0001796089491108432</v>
+        <v>0.04394926875829697</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.000645422434899956</v>
+        <v>0.01162976864725351</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0002144256432075053</v>
+        <v>0.006938068196177483</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0003716929350048304</v>
+        <v>0.05685645341873169</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.0006648232229053974</v>
+        <v>0.07554806023836136</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0009401493007317185</v>
+        <v>0.0371692106127739</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0004073236777912825</v>
+        <v>0.09749887883663177</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0003558514872565866</v>
+        <v>0.03580935299396515</v>
       </c>
       <c r="FM15" t="n">
-        <v>6.135036528576165e-05</v>
+        <v>0.0158009622246027</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0004498170455917716</v>
+        <v>0.0758214145898819</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0006940293242223561</v>
+        <v>0.09148608893156052</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0006686566048301756</v>
+        <v>0.07721873372793198</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0006016581319272518</v>
+        <v>0.05772165209054947</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.001116358442232013</v>
+        <v>0.1712187230587006</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0009709644946269691</v>
+        <v>0.1592019647359848</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0009642314398661256</v>
+        <v>0.1364858746528625</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0003959905880037695</v>
+        <v>0.1546930223703384</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0004366606008261442</v>
+        <v>0.05480905249714851</v>
       </c>
       <c r="FW15" t="n">
-        <v>8.964857261162251e-05</v>
+        <v>0.176297128200531</v>
       </c>
       <c r="FX15" t="n">
-        <v>9.338741801911965e-05</v>
+        <v>0.08632925152778625</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.001188927562907338</v>
+        <v>0.02588682435452938</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0001946797710843384</v>
+        <v>0.05178483575582504</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0002214877313235775</v>
+        <v>0.03490811958909035</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0002844918926712126</v>
+        <v>0.02390025556087494</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.001963507616892457</v>
+        <v>0.1110286563634872</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.001396470353938639</v>
+        <v>0.1322105079889297</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.002442928031086922</v>
+        <v>0.08636775612831116</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0006038701976649463</v>
+        <v>0.06603264063596725</v>
       </c>
       <c r="GG15" t="n">
-        <v>3.558197931852192e-05</v>
+        <v>0.02805354259908199</v>
       </c>
     </row>
   </sheetData>
